--- a/examples/troponin_I/Troponin_I_SDTM.xlsx
+++ b/examples/troponin_I/Troponin_I_SDTM.xlsx
@@ -681,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J97"/>
+  <dimension ref="A1:J100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -703,6 +703,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -845,6 +846,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
@@ -852,6 +854,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
@@ -981,6 +984,7 @@
       <c r="H18" s="14" t="n"/>
       <c r="I18" s="12" t="n"/>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
@@ -1547,7 +1551,7 @@
           <t>Unique identifier for a study.</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr"/>
+      <c r="G32" s="5" t="n"/>
       <c r="H32" s="6" t="inlineStr">
         <is>
           <t>Req</t>
@@ -1595,7 +1599,7 @@
           <t>Two-character abbreviation for the domain.</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr"/>
+      <c r="G33" s="5" t="n"/>
       <c r="H33" s="6" t="inlineStr">
         <is>
           <t>Req</t>
@@ -1643,7 +1647,7 @@
           <t>Identifier used to uniquely identify a subject across all studies for all applications or submissions involving the product.</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr"/>
+      <c r="G34" s="5" t="n"/>
       <c r="H34" s="6" t="inlineStr">
         <is>
           <t>Req</t>
@@ -1795,7 +1799,7 @@
           <t>Internal or external specimen identifier. Example: specimen ID.</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr"/>
+      <c r="G37" s="5" t="n"/>
       <c r="H37" s="6" t="inlineStr">
         <is>
           <t>Perm</t>
@@ -1843,7 +1847,11 @@
           <t>Short name of the measurement, test, or examination described in LBTEST. It can be used as a column name when converting a dataset from a vertical to a horizontal format. The value in LBTESTCD cannot be longer than 8 characters, nor can it start with a number (e.g., "1TEST" is not valid). LBTESTCD cannot contain characters other than letters, numbers, or underscores. Examples: "ALT", "LDH".</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr"/>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>CDISC CT: TROPONI3 = Troponin I Type 3 (cardiac troponin I, C135448).</t>
+        </is>
+      </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
           <t>Req</t>
@@ -1891,7 +1899,7 @@
           <t>Verbatim name of the test or examination used to obtain the measurement or finding. Note: Any test normally performed by a clinical laboratory is considered a lab test. The value in LBTEST cannot be longer than 40 characters. Examples: "Alanine Aminotransferase", "Lactate Dehydrogenase".</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr"/>
+      <c r="G39" s="5" t="n"/>
       <c r="H39" s="6" t="inlineStr">
         <is>
           <t>Req</t>
@@ -1939,7 +1947,7 @@
           <t>Used to define a category of related records across subjects. Examples: "HEMATOLOGY", "URINALYSIS", "CHEMISTRY".</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr"/>
+      <c r="G40" s="5" t="n"/>
       <c r="H40" s="6" t="inlineStr">
         <is>
           <t>Exp</t>
@@ -2039,7 +2047,7 @@
           <t>Original units in which the data were collected. The unit for LBORRES. Example: "g/L".</t>
         </is>
       </c>
-      <c r="G42" s="5" t="inlineStr"/>
+      <c r="G42" s="5" t="n"/>
       <c r="H42" s="6" t="inlineStr">
         <is>
           <t>Exp</t>
@@ -2062,45 +2070,45 @@
           <t>LB</t>
         </is>
       </c>
-      <c r="B43" s="20" t="inlineStr">
-        <is>
-          <t>LBSTRESC</t>
+      <c r="B43" s="22" t="inlineStr">
+        <is>
+          <t>LBLLOD</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Character Result/Finding in Std Format</t>
+          <t>Lower Limit of Detection</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>Result Qualifier</t>
-        </is>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>C117222</t>
-        </is>
-      </c>
+          <t>Variable Qualifier</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="n"/>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Contains the result value for all findings, copied or derived from LBORRES in a standard format or standard units. LBSTRESC should store all results or findings in character format; if results are numeric, they should also be stored in numeric format in LBSTRESN. For example, if a test has results "NONE", "NEG", and "NEGATIVE" in LBORRES and these results effectively have the same meaning, they could be represented in standard format in LBSTRESC as "NEGATIVE". For other examples, see Original and Standardized Results.</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="inlineStr"/>
+          <t>The lowest threshold (as originally received or collected) for reliably detecting the presence or absence of substance measured by a specific test.</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Moved here from SUPPLB.LBLOD: SDTMIG v3.4 §8.4.4 does not allow a supplemental qualifier for data a standard variable holds.</t>
+        </is>
+      </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>Exp</t>
+          <t>Perm</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>SDTMIG v3.4 (LB.LBSTRESC)</t>
-        </is>
-      </c>
-      <c r="J43" s="21" t="inlineStr">
-        <is>
-          <t>S</t>
+          <t>SDTMIG v3.4 (LB.LBLLOD)</t>
+        </is>
+      </c>
+      <c r="J43" s="23" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -2112,12 +2120,12 @@
       </c>
       <c r="B44" s="20" t="inlineStr">
         <is>
-          <t>LBSTRESN</t>
+          <t>LBSTRESC</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Numeric Result/Finding in Standard Units</t>
+          <t>Character Result/Finding in Std Format</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
@@ -2127,19 +2135,15 @@
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>C171009</t>
+          <t>C117222</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Used for continuous or numeric results or findings in standard format; copied in numeric format from LBSTRESC. LBSTRESN should store all numeric test results or findings.</t>
-        </is>
-      </c>
-      <c r="G44" s="5" t="inlineStr">
-        <is>
-          <t>Empty when the result is not a clean number.</t>
-        </is>
-      </c>
+          <t>Contains the result value for all findings, copied or derived from LBORRES in a standard format or standard units. LBSTRESC should store all results or findings in character format; if results are numeric, they should also be stored in numeric format in LBSTRESN. For example, if a test has results "NONE", "NEG", and "NEGATIVE" in LBORRES and these results effectively have the same meaning, they could be represented in standard format in LBSTRESC as "NEGATIVE". For other examples, see Original and Standardized Results.</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="n"/>
       <c r="H44" s="6" t="inlineStr">
         <is>
           <t>Exp</t>
@@ -2147,7 +2151,7 @@
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>SDTMIG v3.4 (LB.LBSTRESN)</t>
+          <t>SDTMIG v3.4 (LB.LBSTRESC)</t>
         </is>
       </c>
       <c r="J44" s="21" t="inlineStr">
@@ -2162,32 +2166,36 @@
           <t>LB</t>
         </is>
       </c>
-      <c r="B45" s="22" t="inlineStr">
-        <is>
-          <t>LBSTRESU</t>
+      <c r="B45" s="20" t="inlineStr">
+        <is>
+          <t>LBSTRESN</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Standard Units</t>
+          <t>Numeric Result/Finding in Standard Units</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>Variable Qualifier</t>
+          <t>Result Qualifier</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>C82587</t>
+          <t>C171009</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Standardized unit used for LBSTRESC or LBSTRESN.</t>
-        </is>
-      </c>
-      <c r="G45" s="5" t="inlineStr"/>
+          <t>Used for continuous or numeric results or findings in standard format; copied in numeric format from LBSTRESC. LBSTRESN should store all numeric test results or findings.</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>Empty when the result is not a clean number.</t>
+        </is>
+      </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
           <t>Exp</t>
@@ -2195,12 +2203,12 @@
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>SDTMIG v3.4 (LB.LBSTRESU)</t>
-        </is>
-      </c>
-      <c r="J45" s="23" t="inlineStr">
-        <is>
-          <t>T</t>
+          <t>SDTMIG v3.4 (LB.LBSTRESN)</t>
+        </is>
+      </c>
+      <c r="J45" s="21" t="inlineStr">
+        <is>
+          <t>S</t>
         </is>
       </c>
     </row>
@@ -2212,12 +2220,12 @@
       </c>
       <c r="B46" s="22" t="inlineStr">
         <is>
-          <t>LBSTNRHI</t>
+          <t>LBSTRESU</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Reference Range Upper Limit-Std Units</t>
+          <t>Standard Units</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -2227,15 +2235,15 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>C171007</t>
+          <t>C82587</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Upper end of reference range for continuous measurements in standardized units. Should be populated only for continuous results.</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr"/>
+          <t>Standardized unit used for LBSTRESC or LBSTRESN.</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="n"/>
       <c r="H46" s="6" t="inlineStr">
         <is>
           <t>Exp</t>
@@ -2243,7 +2251,7 @@
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>SDTMIG v3.4 (LB.LBSTNRHI)</t>
+          <t>SDTMIG v3.4 (LB.LBSTRESU)</t>
         </is>
       </c>
       <c r="J46" s="23" t="inlineStr">
@@ -2258,14 +2266,14 @@
           <t>LB</t>
         </is>
       </c>
-      <c r="B47" s="20" t="inlineStr">
-        <is>
-          <t>LBNRIND</t>
+      <c r="B47" s="22" t="inlineStr">
+        <is>
+          <t>LBSTNRLO</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Reference Range Indicator</t>
+          <t>Reference Range Lower Limit-Std Units</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -2273,17 +2281,17 @@
           <t>Variable Qualifier</t>
         </is>
       </c>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>C170999</t>
-        </is>
-      </c>
+      <c r="E47" s="6" t="n"/>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Indicates where the value falls with respect to reference range defined by LBORNRLO and LBORNRHI, LBSTNRLO and LBSTNRHI, or by LBSTNRC. Examples: "NORMAL", "ABNORMAL", "HIGH", "LOW". Sponsors should specify in the study metadata (Comments column in the Define-XML document) whether LBNRIND refers to the original or standard reference ranges and results. LBNRIND is not used to indicate clinical significance.</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="inlineStr"/>
+          <t>Lower end of reference range for continuous measurements in standardized units.</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>Empty here: the 99th-percentile limit is upper only.</t>
+        </is>
+      </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
           <t>Exp</t>
@@ -2291,12 +2299,12 @@
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>SDTMIG v3.4 (LB.LBNRIND)</t>
-        </is>
-      </c>
-      <c r="J47" s="21" t="inlineStr">
-        <is>
-          <t>S</t>
+          <t>SDTMIG v3.4 (LB.LBSTNRLO)</t>
+        </is>
+      </c>
+      <c r="J47" s="23" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -2308,38 +2316,38 @@
       </c>
       <c r="B48" s="22" t="inlineStr">
         <is>
-          <t>LBSPEC</t>
+          <t>LBSTNRHI</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Specimen Type</t>
+          <t>Reference Range Upper Limit-Std Units</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>Record Qualifier</t>
+          <t>Variable Qualifier</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>C70713</t>
+          <t>C171007</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>Defines the type of specimen used for a measurement. Examples: "SERUM", "PLASMA", "URINE".</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr"/>
+          <t>Upper end of reference range for continuous measurements in standardized units. Should be populated only for continuous results.</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="n"/>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>Perm</t>
+          <t>Exp</t>
         </is>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
-          <t>SDTMIG v3.4 (LB.LBSPEC)</t>
+          <t>SDTMIG v3.4 (LB.LBSTNRHI)</t>
         </is>
       </c>
       <c r="J48" s="23" t="inlineStr">
@@ -2354,41 +2362,45 @@
           <t>LB</t>
         </is>
       </c>
-      <c r="B49" s="22" t="inlineStr">
-        <is>
-          <t>LBMETHOD</t>
+      <c r="B49" s="20" t="inlineStr">
+        <is>
+          <t>LBNRIND</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Method of Test or Examination</t>
+          <t>Reference Range Indicator</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>Record Qualifier</t>
-        </is>
-      </c>
-      <c r="E49" s="6" t="inlineStr"/>
+          <t>Variable Qualifier</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>C170999</t>
+        </is>
+      </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Method of the test or examination. Examples: "EIA" (enzyme immunoassay), "ELECTROPHORESIS", "DIPSTICK".</t>
-        </is>
-      </c>
-      <c r="G49" s="5" t="inlineStr"/>
+          <t>Indicates where the value falls with respect to reference range defined by LBORNRLO and LBORNRHI, LBSTNRLO and LBSTNRHI, or by LBSTNRC. Examples: "NORMAL", "ABNORMAL", "HIGH", "LOW". Sponsors should specify in the study metadata (Comments column in the Define-XML document) whether LBNRIND refers to the original or standard reference ranges and results. LBNRIND is not used to indicate clinical significance.</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="n"/>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>Perm</t>
+          <t>Exp</t>
         </is>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>SDTMIG v3.4 (LB.LBMETHOD)</t>
-        </is>
-      </c>
-      <c r="J49" s="23" t="inlineStr">
-        <is>
-          <t>T</t>
+          <t>SDTMIG v3.4 (LB.LBNRIND)</t>
+        </is>
+      </c>
+      <c r="J49" s="21" t="inlineStr">
+        <is>
+          <t>S</t>
         </is>
       </c>
     </row>
@@ -2400,12 +2412,12 @@
       </c>
       <c r="B50" s="22" t="inlineStr">
         <is>
-          <t>LBNAM</t>
+          <t>LBSPEC</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Vendor Name</t>
+          <t>Specimen Type</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -2415,19 +2427,15 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>C117200</t>
+          <t>C70713</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>The name or identifier of the laboratory that performed the test.</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="inlineStr">
-        <is>
-          <t>Holds the manufacturer here. The assay/kit name has no LB variable and sits in SUPPLB.</t>
-        </is>
-      </c>
+          <t>Defines the type of specimen used for a measurement. Examples: "SERUM", "PLASMA", "URINE".</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="n"/>
       <c r="H50" s="6" t="inlineStr">
         <is>
           <t>Perm</t>
@@ -2435,7 +2443,7 @@
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
-          <t>SDTMIG v3.4 (LB.LBNAM)</t>
+          <t>SDTMIG v3.4 (LB.LBSPEC)</t>
         </is>
       </c>
       <c r="J50" s="23" t="inlineStr">
@@ -2452,30 +2460,26 @@
       </c>
       <c r="B51" s="22" t="inlineStr">
         <is>
-          <t>LBLOINC</t>
+          <t>LBMETHOD</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>LOINC Code</t>
+          <t>Method of Test or Examination</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Synonym Qualifier</t>
-        </is>
-      </c>
-      <c r="E51" s="6" t="inlineStr">
-        <is>
-          <t>C82502</t>
-        </is>
-      </c>
+          <t>Record Qualifier</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="n"/>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Code for the lab test from the LOINC code system. The sponsor is expected to provide the dictionary name and version used to map the terms utilizing the Define-XML external codelist attributes.</t>
-        </is>
-      </c>
-      <c r="G51" s="5" t="inlineStr"/>
+          <t>Method of the test or examination. Examples: "EIA" (enzyme immunoassay), "ELECTROPHORESIS", "DIPSTICK".</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="n"/>
       <c r="H51" s="6" t="inlineStr">
         <is>
           <t>Perm</t>
@@ -2483,7 +2487,7 @@
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>SDTMIG v3.4 (LB.LBLOINC)</t>
+          <t>SDTMIG v3.4 (LB.LBMETHOD)</t>
         </is>
       </c>
       <c r="J51" s="23" t="inlineStr">
@@ -2500,30 +2504,34 @@
       </c>
       <c r="B52" s="22" t="inlineStr">
         <is>
-          <t>VISIT</t>
+          <t>LBNAM</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Visit Name</t>
+          <t>Vendor Name</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>Timing</t>
+          <t>Record Qualifier</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>C171010</t>
+          <t>C117200</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Protocol-defined description of clinical encounter. May be used in addition to VISITNUM and/or VISITDY.</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="inlineStr"/>
+          <t>The name or identifier of the laboratory that performed the test.</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>Holds the manufacturer here. The assay/kit name has no LB variable and sits in SUPPLB.</t>
+        </is>
+      </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
           <t>Perm</t>
@@ -2531,7 +2539,7 @@
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
-          <t>SDTMIG v3.4 (LB.VISIT)</t>
+          <t>SDTMIG v3.4 (LB.LBNAM)</t>
         </is>
       </c>
       <c r="J52" s="23" t="inlineStr">
@@ -2546,32 +2554,32 @@
           <t>LB</t>
         </is>
       </c>
-      <c r="B53" s="20" t="inlineStr">
-        <is>
-          <t>LBBLFL</t>
+      <c r="B53" s="22" t="inlineStr">
+        <is>
+          <t>LBLOINC</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Baseline Flag</t>
+          <t>LOINC Code</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Record Qualifier</t>
+          <t>Synonym Qualifier</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>C82526</t>
+          <t>C82502</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Indicator used to identify a baseline value. Should be "Y" or null. Note that LBBLFL is retained for backward compatibility. The authoritative baseline for statistical analysis is in an ADaM dataset.</t>
-        </is>
-      </c>
-      <c r="G53" s="5" t="inlineStr"/>
+          <t>Code for the lab test from the LOINC code system. The sponsor is expected to provide the dictionary name and version used to map the terms utilizing the Define-XML external codelist attributes.</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="n"/>
       <c r="H53" s="6" t="inlineStr">
         <is>
           <t>Perm</t>
@@ -2579,12 +2587,12 @@
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>SDTMIG v3.4 (LB.LBBLFL)</t>
-        </is>
-      </c>
-      <c r="J53" s="21" t="inlineStr">
-        <is>
-          <t>S</t>
+          <t>SDTMIG v3.4 (LB.LBLOINC)</t>
+        </is>
+      </c>
+      <c r="J53" s="23" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -2594,32 +2602,32 @@
           <t>LB</t>
         </is>
       </c>
-      <c r="B54" s="24" t="inlineStr">
-        <is>
-          <t>LBDTC</t>
+      <c r="B54" s="22" t="inlineStr">
+        <is>
+          <t>LBLOBXFL</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Date/Time of Specimen Collection</t>
+          <t>Last Observation Before Exposure Flag</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>Timing</t>
-        </is>
-      </c>
-      <c r="E54" s="6" t="inlineStr">
-        <is>
-          <t>C82515</t>
-        </is>
-      </c>
+          <t>Record Qualifier</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="n"/>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Date/time of specimen collection represented in ISO 8601 character format.</t>
-        </is>
-      </c>
-      <c r="G54" s="5" t="inlineStr"/>
+          <t>Operationally derived indicator used to identify the last non-missing value prior to RFXSTDTC. The value should be "Y" or null.</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>Null throughout: this observational study gives no medical product, so there is no RFXSTDTC.</t>
+        </is>
+      </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
           <t>Exp</t>
@@ -2627,55 +2635,59 @@
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
-          <t>SDTMIG v3.4 (LB.LBDTC)</t>
-        </is>
-      </c>
-      <c r="J54" s="25" t="inlineStr">
-        <is>
-          <t>R</t>
+          <t>SDTMIG v3.4 (LB.LBLOBXFL)</t>
+        </is>
+      </c>
+      <c r="J54" s="21" t="inlineStr">
+        <is>
+          <t>S</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="19" t="inlineStr">
-        <is>
-          <t>SUPPLB</t>
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>LB</t>
         </is>
       </c>
       <c r="B55" s="20" t="inlineStr">
         <is>
-          <t>STUDYID</t>
+          <t>LBBLFL</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Study Identifier</t>
+          <t>Baseline Flag</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Identifier</t>
+          <t>Record Qualifier</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>C83082</t>
+          <t>C82526</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Study identifier of the parent record(s).</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="inlineStr"/>
+          <t>Indicator used to identify a baseline value. Should be "Y" or null. Note that LBBLFL is retained for backward compatibility. The authoritative baseline for statistical analysis is in an ADaM dataset.</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>Y on the first result per subject, otherwise null; SDTMIG allows only Y or null.</t>
+        </is>
+      </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>Req</t>
+          <t>Perm</t>
         </is>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
-          <t>SDTMIG v3.4 (SUPPQUAL.STUDYID)</t>
+          <t>SDTMIG v3.4 (LB.LBBLFL)</t>
         </is>
       </c>
       <c r="J55" s="21" t="inlineStr">
@@ -2687,123 +2699,127 @@
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>SUPPLB</t>
-        </is>
-      </c>
-      <c r="B56" s="20" t="inlineStr">
-        <is>
-          <t>RDOMAIN</t>
+          <t>LB</t>
+        </is>
+      </c>
+      <c r="B56" s="22" t="inlineStr">
+        <is>
+          <t>LBLLOQ</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Related Domain Abbreviation</t>
+          <t>Lower Limit of Quantitation</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>Identifier</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="inlineStr"/>
+          <t>Variable Qualifier</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="n"/>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>Two-character abbreviation for the domain of the parent record(s).</t>
-        </is>
-      </c>
-      <c r="G56" s="5" t="inlineStr"/>
+          <t>Indicates the lower limit of quantitation for an assay. Units will be those used for LBSTRESU.</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>Findings-class qualifier (--LLOQ), added under LB assumption 5; moved here from SUPPLB.LBLLOQ.</t>
+        </is>
+      </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>Req</t>
+          <t>Perm</t>
         </is>
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
-          <t>SDTMIG v3.4 (SUPPQUAL.RDOMAIN)</t>
-        </is>
-      </c>
-      <c r="J56" s="21" t="inlineStr">
-        <is>
-          <t>S</t>
+          <t>SDTM v2.1 (--LLOQ)</t>
+        </is>
+      </c>
+      <c r="J56" s="23" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>SUPPLB</t>
-        </is>
-      </c>
-      <c r="B57" s="20" t="inlineStr">
-        <is>
-          <t>USUBJID</t>
+          <t>LB</t>
+        </is>
+      </c>
+      <c r="B57" s="22" t="inlineStr">
+        <is>
+          <t>LBULOQ</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Unique Subject Identifier</t>
+          <t>Upper Limit of Quantitation</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Identifier</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="inlineStr">
-        <is>
-          <t>C69256</t>
-        </is>
-      </c>
+          <t>Variable Qualifier</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="n"/>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Identifier used to uniquely identify a subject across all studies for all applications or submissions involving the product. This is the value of USUBJID in the parent record(s).</t>
-        </is>
-      </c>
-      <c r="G57" s="5" t="inlineStr"/>
+          <t>Indicates the upper limit of quantitation for an assay. Units will be those used for LBSTRESU.</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>Findings-class qualifier (--ULOQ), added under LB assumption 5; moved here from SUPPLB.LBULOQ.</t>
+        </is>
+      </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>Req</t>
+          <t>Perm</t>
         </is>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
-          <t>SDTMIG v3.4 (SUPPQUAL.USUBJID)</t>
-        </is>
-      </c>
-      <c r="J57" s="21" t="inlineStr">
-        <is>
-          <t>S</t>
+          <t>SDTM v2.1 (--ULOQ)</t>
+        </is>
+      </c>
+      <c r="J57" s="23" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>SUPPLB</t>
-        </is>
-      </c>
-      <c r="B58" s="20" t="inlineStr">
-        <is>
-          <t>IDVAR</t>
+          <t>LB</t>
+        </is>
+      </c>
+      <c r="B58" s="22" t="inlineStr">
+        <is>
+          <t>VISITNUM</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Identifying Variable</t>
+          <t>Visit Number</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>Identifier</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="inlineStr"/>
+          <t>Timing</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="n"/>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Identifying variable in the dataset that identifies the related record(s). Examples: --SEQ, --GRPID.</t>
-        </is>
-      </c>
-      <c r="G58" s="5" t="inlineStr"/>
+          <t>Clinical encounter number. Numeric version of VISIT, used for sorting.</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="n"/>
       <c r="H58" s="6" t="inlineStr">
         <is>
           <t>Exp</t>
@@ -2811,128 +2827,140 @@
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
-          <t>SDTMIG v3.4 (SUPPQUAL.IDVAR)</t>
-        </is>
-      </c>
-      <c r="J58" s="21" t="inlineStr">
-        <is>
-          <t>S</t>
+          <t>SDTMIG v3.4 (LB.VISITNUM)</t>
+        </is>
+      </c>
+      <c r="J58" s="23" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>SUPPLB</t>
-        </is>
-      </c>
-      <c r="B59" s="20" t="inlineStr">
-        <is>
-          <t>IDVARVAL</t>
+          <t>LB</t>
+        </is>
+      </c>
+      <c r="B59" s="22" t="inlineStr">
+        <is>
+          <t>VISIT</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Identifying Variable Value</t>
+          <t>Visit Name</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Identifier</t>
-        </is>
-      </c>
-      <c r="E59" s="6" t="inlineStr"/>
+          <t>Timing</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>C171010</t>
+        </is>
+      </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Value of identifying variable of the parent record(s).</t>
-        </is>
-      </c>
-      <c r="G59" s="5" t="inlineStr"/>
+          <t>Protocol-defined description of clinical encounter. May be used in addition to VISITNUM and/or VISITDY.</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="n"/>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>Exp</t>
+          <t>Perm</t>
         </is>
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
-          <t>SDTMIG v3.4 (SUPPQUAL.IDVARVAL)</t>
-        </is>
-      </c>
-      <c r="J59" s="21" t="inlineStr">
-        <is>
-          <t>S</t>
+          <t>SDTMIG v3.4 (LB.VISIT)</t>
+        </is>
+      </c>
+      <c r="J59" s="23" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
+          <t>LB</t>
+        </is>
+      </c>
+      <c r="B60" s="24" t="inlineStr">
+        <is>
+          <t>LBDTC</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>Date/Time of Specimen Collection</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>Timing</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>C82515</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>Date/time of specimen collection represented in ISO 8601 character format.</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="n"/>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>Exp</t>
+        </is>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>SDTMIG v3.4 (LB.LBDTC)</t>
+        </is>
+      </c>
+      <c r="J60" s="25" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="19" t="inlineStr">
+        <is>
           <t>SUPPLB</t>
         </is>
       </c>
-      <c r="B60" s="20" t="inlineStr">
-        <is>
-          <t>QNAM</t>
-        </is>
-      </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>Qualifier Variable Name</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>Topic</t>
-        </is>
-      </c>
-      <c r="E60" s="6" t="inlineStr"/>
-      <c r="F60" s="5" t="inlineStr">
-        <is>
-          <t>The short name of the qualifier variable, which is used as a column name in a domain view with data from the parent domain. The value in QNAM cannot be longer than 8 characters, nor can it start with a number (e.g., "1TEST" is not valid). QNAM cannot contain characters other than letters, numbers, or underscores. This will often be the column name in the sponsor's operational dataset.</t>
-        </is>
-      </c>
-      <c r="G60" s="5" t="inlineStr"/>
-      <c r="H60" s="6" t="inlineStr">
-        <is>
-          <t>Req</t>
-        </is>
-      </c>
-      <c r="I60" s="6" t="inlineStr">
-        <is>
-          <t>SDTMIG v3.4 (SUPPQUAL.QNAM)</t>
-        </is>
-      </c>
-      <c r="J60" s="21" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>SUPPLB</t>
-        </is>
-      </c>
       <c r="B61" s="20" t="inlineStr">
         <is>
-          <t>QLABEL</t>
+          <t>STUDYID</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Qualifier Variable Label</t>
+          <t>Study Identifier</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Synonym Qualifier</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="inlineStr"/>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>C83082</t>
+        </is>
+      </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>This is the long name or label associated with QNAM. The value in QLABEL cannot be longer than 40 characters. This will often be the column label in the sponsor's original dataset.</t>
+          <t>Study identifier of the parent record(s).</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr"/>
@@ -2943,7 +2971,7 @@
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
-          <t>SDTMIG v3.4 (SUPPQUAL.QLABEL)</t>
+          <t>SDTMIG v3.4 (SUPPQUAL.STUDYID)</t>
         </is>
       </c>
       <c r="J61" s="21" t="inlineStr">
@@ -2960,30 +2988,26 @@
       </c>
       <c r="B62" s="20" t="inlineStr">
         <is>
-          <t>QVAL</t>
+          <t>RDOMAIN</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Data Value</t>
+          <t>Related Domain Abbreviation</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>Result Qualifier</t>
+          <t>Identifier</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr"/>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>Result of, response to, or value associated with QNAM. A value for this column is required; no records can be in SUPP-- with a null value for QVAL.</t>
-        </is>
-      </c>
-      <c r="G62" s="5" t="inlineStr">
-        <is>
-          <t>Always stored as text, whatever the real type.</t>
-        </is>
-      </c>
+          <t>Two-character abbreviation for the domain of the parent record(s).</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr"/>
       <c r="H62" s="6" t="inlineStr">
         <is>
           <t>Req</t>
@@ -2991,7 +3015,7 @@
       </c>
       <c r="I62" s="6" t="inlineStr">
         <is>
-          <t>SDTMIG v3.4 (SUPPQUAL.QVAL)</t>
+          <t>SDTMIG v3.4 (SUPPQUAL.RDOMAIN)</t>
         </is>
       </c>
       <c r="J62" s="21" t="inlineStr">
@@ -3008,23 +3032,27 @@
       </c>
       <c r="B63" s="20" t="inlineStr">
         <is>
-          <t>QORIG</t>
+          <t>USUBJID</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Origin</t>
+          <t>Unique Subject Identifier</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Record Qualifier</t>
-        </is>
-      </c>
-      <c r="E63" s="6" t="inlineStr"/>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>C69256</t>
+        </is>
+      </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Because QVAL can represent a mixture of collected (on a CRF), derived, or assigned items, QORIG is used to indicate the origin of this data. Examples: "CRF", "Assigned", "Derived". See Section 4.1.8, Origin Metadata.</t>
+          <t>Identifier used to uniquely identify a subject across all studies for all applications or submissions involving the product. This is the value of USUBJID in the parent record(s).</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr"/>
@@ -3035,7 +3063,7 @@
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
-          <t>SDTMIG v3.4 (SUPPQUAL.QORIG)</t>
+          <t>SDTMIG v3.4 (SUPPQUAL.USUBJID)</t>
         </is>
       </c>
       <c r="J63" s="21" t="inlineStr">
@@ -3052,23 +3080,23 @@
       </c>
       <c r="B64" s="20" t="inlineStr">
         <is>
-          <t>QEVAL</t>
+          <t>IDVAR</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Evaluator</t>
+          <t>Identifying Variable</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>Record Qualifier</t>
+          <t>Identifier</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr"/>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Used only for results that are subjective (e.g., assigned by a person or a group). Should be null for records that contain objectively collected or derived data. Examples: "ADJUDICATION COMMITTEE", "STATISTICIAN", "DATABASE ADMINISTRATOR", "CLINICAL COORDINATOR".</t>
+          <t>Identifying variable in the dataset that identifies the related record(s). Examples: --SEQ, --GRPID.</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr"/>
@@ -3079,7 +3107,7 @@
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
-          <t>SDTMIG v3.4 (SUPPQUAL.QEVAL)</t>
+          <t>SDTMIG v3.4 (SUPPQUAL.IDVAR)</t>
         </is>
       </c>
       <c r="J64" s="21" t="inlineStr">
@@ -3089,19 +3117,19 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="19" t="inlineStr">
-        <is>
-          <t>BM</t>
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>SUPPLB</t>
         </is>
       </c>
       <c r="B65" s="20" t="inlineStr">
         <is>
-          <t>STUDYID</t>
+          <t>IDVARVAL</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Study Identifier</t>
+          <t>Identifying Variable Value</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -3112,18 +3140,18 @@
       <c r="E65" s="6" t="inlineStr"/>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>Unique identifier for the study.</t>
+          <t>Value of identifying variable of the parent record(s).</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr"/>
-      <c r="H65" s="7" t="inlineStr">
-        <is>
-          <t>Proposed</t>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>Exp</t>
         </is>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
-          <t>Proposed - not in SDTMIG v3.4</t>
+          <t>SDTMIG v3.4 (SUPPQUAL.IDVARVAL)</t>
         </is>
       </c>
       <c r="J65" s="21" t="inlineStr">
@@ -3135,39 +3163,39 @@
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>BM</t>
+          <t>SUPPLB</t>
         </is>
       </c>
       <c r="B66" s="20" t="inlineStr">
         <is>
-          <t>DOMAIN</t>
+          <t>QNAM</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Domain Abbreviation</t>
+          <t>Qualifier Variable Name</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>Identifier</t>
+          <t>Topic</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr"/>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>Always 'BM'.</t>
+          <t>The short name of the qualifier variable, which is used as a column name in a domain view with data from the parent domain. The value in QNAM cannot be longer than 8 characters, nor can it start with a number (e.g., "1TEST" is not valid). QNAM cannot contain characters other than letters, numbers, or underscores. This will often be the column name in the sponsor's operational dataset.</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr"/>
-      <c r="H66" s="7" t="inlineStr">
-        <is>
-          <t>Proposed</t>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>Req</t>
         </is>
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
-          <t>Proposed - not in SDTMIG v3.4</t>
+          <t>SDTMIG v3.4 (SUPPQUAL.QNAM)</t>
         </is>
       </c>
       <c r="J66" s="21" t="inlineStr">
@@ -3179,204 +3207,208 @@
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>BM</t>
-        </is>
-      </c>
-      <c r="B67" s="26" t="inlineStr">
-        <is>
-          <t>BMID</t>
+          <t>SUPPLB</t>
+        </is>
+      </c>
+      <c r="B67" s="20" t="inlineStr">
+        <is>
+          <t>QLABEL</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Biomarker Context Identifier</t>
+          <t>Qualifier Variable Label</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>Identifier</t>
+          <t>Synonym Qualifier</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr"/>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Identifier for this biomarker claim. What other records and documents cite.</t>
+          <t>This is the long name or label associated with QNAM. The value in QLABEL cannot be longer than 40 characters. This will often be the column label in the sponsor's original dataset.</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr"/>
-      <c r="H67" s="7" t="inlineStr">
-        <is>
-          <t>Proposed</t>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>Req</t>
         </is>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
-          <t>Proposed - not in SDTMIG v3.4</t>
-        </is>
-      </c>
-      <c r="J67" s="27" t="inlineStr">
-        <is>
-          <t>K</t>
+          <t>SDTMIG v3.4 (SUPPQUAL.QLABEL)</t>
+        </is>
+      </c>
+      <c r="J67" s="21" t="inlineStr">
+        <is>
+          <t>S</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>BM</t>
-        </is>
-      </c>
-      <c r="B68" s="28" t="inlineStr">
-        <is>
-          <t>BMVER</t>
+          <t>SUPPLB</t>
+        </is>
+      </c>
+      <c r="B68" s="20" t="inlineStr">
+        <is>
+          <t>QVAL</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Biomarker Context Version</t>
+          <t>Data Value</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>Identifier</t>
+          <t>Result Qualifier</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr"/>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>Version of the claim. Changing a rule, role or population increments this rather than overwriting what was previously asserted.</t>
-        </is>
-      </c>
-      <c r="G68" s="5" t="inlineStr"/>
-      <c r="H68" s="7" t="inlineStr">
-        <is>
-          <t>Proposed</t>
+          <t>Result of, response to, or value associated with QNAM. A value for this column is required; no records can be in SUPP-- with a null value for QVAL.</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>Always stored as text, whatever the real type.</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>Req</t>
         </is>
       </c>
       <c r="I68" s="6" t="inlineStr">
         <is>
-          <t>Proposed - not in SDTMIG v3.4</t>
-        </is>
-      </c>
-      <c r="J68" s="29" t="inlineStr">
-        <is>
-          <t>N</t>
+          <t>SDTMIG v3.4 (SUPPQUAL.QVAL)</t>
+        </is>
+      </c>
+      <c r="J68" s="21" t="inlineStr">
+        <is>
+          <t>S</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>BM</t>
-        </is>
-      </c>
-      <c r="B69" s="26" t="inlineStr">
-        <is>
-          <t>BMENTNM</t>
+          <t>SUPPLB</t>
+        </is>
+      </c>
+      <c r="B69" s="20" t="inlineStr">
+        <is>
+          <t>QORIG</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Entity Name</t>
+          <t>Origin</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Topic</t>
+          <t>Record Qualifier</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr"/>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>The molecule or feature being used as a biomarker.</t>
+          <t>Because QVAL can represent a mixture of collected (on a CRF), derived, or assigned items, QORIG is used to indicate the origin of this data. Examples: "CRF", "Assigned", "Derived". See Section 4.1.8, Origin Metadata.</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr"/>
-      <c r="H69" s="7" t="inlineStr">
-        <is>
-          <t>Proposed</t>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>Req</t>
         </is>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
-          <t>Proposed - not in SDTMIG v3.4</t>
-        </is>
-      </c>
-      <c r="J69" s="27" t="inlineStr">
-        <is>
-          <t>K</t>
+          <t>SDTMIG v3.4 (SUPPQUAL.QORIG)</t>
+        </is>
+      </c>
+      <c r="J69" s="21" t="inlineStr">
+        <is>
+          <t>S</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>BM</t>
-        </is>
-      </c>
-      <c r="B70" s="26" t="inlineStr">
-        <is>
-          <t>BMENTID</t>
+          <t>SUPPLB</t>
+        </is>
+      </c>
+      <c r="B70" s="20" t="inlineStr">
+        <is>
+          <t>QEVAL</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Entity Identifier</t>
+          <t>Evaluator</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>Synonym Qualifier</t>
+          <t>Record Qualifier</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr"/>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>Ontology CURIE for the entity: UniProt, HGNC, ChEBI.</t>
+          <t>Used only for results that are subjective (e.g., assigned by a person or a group). Should be null for records that contain objectively collected or derived data. Examples: "ADJUDICATION COMMITTEE", "STATISTICIAN", "DATABASE ADMINISTRATOR", "CLINICAL COORDINATOR".</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr"/>
-      <c r="H70" s="7" t="inlineStr">
-        <is>
-          <t>Proposed</t>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>Exp</t>
         </is>
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
-          <t>Proposed - not in SDTMIG v3.4</t>
-        </is>
-      </c>
-      <c r="J70" s="27" t="inlineStr">
-        <is>
-          <t>K</t>
+          <t>SDTMIG v3.4 (SUPPQUAL.QEVAL)</t>
+        </is>
+      </c>
+      <c r="J70" s="21" t="inlineStr">
+        <is>
+          <t>S</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="6" t="inlineStr">
+      <c r="A71" s="19" t="inlineStr">
         <is>
           <t>BM</t>
         </is>
       </c>
-      <c r="B71" s="26" t="inlineStr">
-        <is>
-          <t>BMENTTP</t>
+      <c r="B71" s="20" t="inlineStr">
+        <is>
+          <t>STUDYID</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Entity Type</t>
+          <t>Study Identifier</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>Grouping Qualifier</t>
+          <t>Identifier</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr"/>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Class of entity: protein, gene, metabolite, cell, derived score.</t>
+          <t>Unique identifier for the study.</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr"/>
@@ -3390,9 +3422,9 @@
           <t>Proposed - not in SDTMIG v3.4</t>
         </is>
       </c>
-      <c r="J71" s="27" t="inlineStr">
-        <is>
-          <t>K</t>
+      <c r="J71" s="21" t="inlineStr">
+        <is>
+          <t>S</t>
         </is>
       </c>
     </row>
@@ -3402,25 +3434,25 @@
           <t>BM</t>
         </is>
       </c>
-      <c r="B72" s="26" t="inlineStr">
-        <is>
-          <t>BMCVTERM</t>
+      <c r="B72" s="20" t="inlineStr">
+        <is>
+          <t>DOMAIN</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Controlled Vocabulary Term</t>
+          <t>Domain Abbreviation</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>Synonym Qualifier</t>
+          <t>Identifier</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr"/>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>The biomarker as a controlled-vocabulary statement composing change, aspect and entity, e.g. 'Increased level of protein TNNI3/UPKB:P19429'. Matches BiomarkerKB biomarker_controlled_vocab and is the string that identifies the biomarker in that resource. The change component (increased, decreased) and the aspect (level, activity, presence) are carried only inside this string; neither is held atomically in BM. The underlying property is implied by the units on the referenced LB records.</t>
+          <t>Always 'BM'.</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr"/>
@@ -3434,9 +3466,9 @@
           <t>Proposed - not in SDTMIG v3.4</t>
         </is>
       </c>
-      <c r="J72" s="27" t="inlineStr">
-        <is>
-          <t>K</t>
+      <c r="J72" s="21" t="inlineStr">
+        <is>
+          <t>S</t>
         </is>
       </c>
     </row>
@@ -3448,23 +3480,23 @@
       </c>
       <c r="B73" s="26" t="inlineStr">
         <is>
-          <t>BMROLE</t>
+          <t>BMID</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>BEST Biomarker Role</t>
+          <t>Biomarker Context Identifier</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Record Qualifier</t>
+          <t>Identifier</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr"/>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>diagnostic, prognostic, monitoring, predictive, safety, susceptibility/risk. Only interpretable alongside BMCOND.</t>
+          <t>Identifier for this biomarker claim. What other records and documents cite.</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr"/>
@@ -3490,25 +3522,25 @@
           <t>BM</t>
         </is>
       </c>
-      <c r="B74" s="26" t="inlineStr">
-        <is>
-          <t>BMCOND</t>
+      <c r="B74" s="28" t="inlineStr">
+        <is>
+          <t>BMVER</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Target Condition or Exposure</t>
+          <t>Biomarker Context Version</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>Record Qualifier</t>
+          <t>Identifier</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr"/>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>The disease or exposure the role is scoped to.</t>
+          <t>Version of the claim. Changing a rule, role or population increments this rather than overwriting what was previously asserted.</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr"/>
@@ -3522,9 +3554,9 @@
           <t>Proposed - not in SDTMIG v3.4</t>
         </is>
       </c>
-      <c r="J74" s="27" t="inlineStr">
-        <is>
-          <t>K</t>
+      <c r="J74" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -3536,23 +3568,23 @@
       </c>
       <c r="B75" s="26" t="inlineStr">
         <is>
-          <t>BMCONDID</t>
+          <t>BMENTNM</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Condition Identifier</t>
+          <t>Entity Name</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>Record Qualifier</t>
+          <t>Topic</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr"/>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>Ontology CURIE for the condition: DOID, MONDO.</t>
+          <t>The molecule or feature being used as a biomarker.</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr"/>
@@ -3578,25 +3610,25 @@
           <t>BM</t>
         </is>
       </c>
-      <c r="B76" s="22" t="inlineStr">
-        <is>
-          <t>BMASSAY</t>
+      <c r="B76" s="26" t="inlineStr">
+        <is>
+          <t>BMENTID</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>Assay Profile Reference</t>
+          <t>Entity Identifier</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>Record Qualifier</t>
+          <t>Synonym Qualifier</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr"/>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>The assay the claim depends on. Decision thresholds are assay-specific and do not transfer between assays.</t>
+          <t>Ontology CURIE for the entity: UniProt, HGNC, ChEBI.</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr"/>
@@ -3610,9 +3642,9 @@
           <t>Proposed - not in SDTMIG v3.4</t>
         </is>
       </c>
-      <c r="J76" s="23" t="inlineStr">
-        <is>
-          <t>T</t>
+      <c r="J76" s="27" t="inlineStr">
+        <is>
+          <t>K</t>
         </is>
       </c>
     </row>
@@ -3622,25 +3654,25 @@
           <t>BM</t>
         </is>
       </c>
-      <c r="B77" s="22" t="inlineStr">
-        <is>
-          <t>BMNAM</t>
+      <c r="B77" s="26" t="inlineStr">
+        <is>
+          <t>BMENTTP</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Assay Manufacturer</t>
+          <t>Entity Type</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>Record Qualifier</t>
+          <t>Grouping Qualifier</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr"/>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>Vendor of the assay named in BMASSAY.</t>
+          <t>Class of entity: protein, gene, metabolite, cell, derived score.</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr"/>
@@ -3654,9 +3686,9 @@
           <t>Proposed - not in SDTMIG v3.4</t>
         </is>
       </c>
-      <c r="J77" s="23" t="inlineStr">
-        <is>
-          <t>T</t>
+      <c r="J77" s="27" t="inlineStr">
+        <is>
+          <t>K</t>
         </is>
       </c>
     </row>
@@ -3666,25 +3698,25 @@
           <t>BM</t>
         </is>
       </c>
-      <c r="B78" s="22" t="inlineStr">
-        <is>
-          <t>BMPLAT</t>
+      <c r="B78" s="26" t="inlineStr">
+        <is>
+          <t>BMCVTERM</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Assay Platform</t>
+          <t>Controlled Vocabulary Term</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>Record Qualifier</t>
+          <t>Synonym Qualifier</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr"/>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>Instrument the assay runs on.</t>
+          <t>The biomarker as a controlled-vocabulary statement composing change, aspect and entity, e.g. 'Increased level of protein TNNI3/UPKB:P19429'. Matches BiomarkerKB biomarker_controlled_vocab and is the string that identifies the biomarker in that resource. The change component (increased, decreased) and the aspect (level, activity, presence) are carried only inside this string; neither is held atomically in BM. The underlying property is implied by the units on the referenced LB records.</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr"/>
@@ -3698,9 +3730,9 @@
           <t>Proposed - not in SDTMIG v3.4</t>
         </is>
       </c>
-      <c r="J78" s="23" t="inlineStr">
-        <is>
-          <t>T</t>
+      <c r="J78" s="27" t="inlineStr">
+        <is>
+          <t>K</t>
         </is>
       </c>
     </row>
@@ -3710,14 +3742,14 @@
           <t>BM</t>
         </is>
       </c>
-      <c r="B79" s="22" t="inlineStr">
-        <is>
-          <t>BMMETHOD</t>
+      <c r="B79" s="26" t="inlineStr">
+        <is>
+          <t>BMROLE</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Measurement Method</t>
+          <t>BEST Biomarker Role</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
@@ -3728,7 +3760,7 @@
       <c r="E79" s="6" t="inlineStr"/>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>The analytical technique, not the product: IMMUNOASSAY, MASS SPECTROMETRY, PCR. The product name is BMASSAY. Modelled on LBMETHOD, which carries the same distinction - putting a vendor assay name here is the commonest error.</t>
+          <t>diagnostic, prognostic, monitoring, predictive, safety, susceptibility/risk. Only interpretable alongside BMCOND.</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr"/>
@@ -3742,9 +3774,9 @@
           <t>Proposed - not in SDTMIG v3.4</t>
         </is>
       </c>
-      <c r="J79" s="23" t="inlineStr">
-        <is>
-          <t>T</t>
+      <c r="J79" s="27" t="inlineStr">
+        <is>
+          <t>K</t>
         </is>
       </c>
     </row>
@@ -3754,14 +3786,14 @@
           <t>BM</t>
         </is>
       </c>
-      <c r="B80" s="22" t="inlineStr">
-        <is>
-          <t>BMSPEC</t>
+      <c r="B80" s="26" t="inlineStr">
+        <is>
+          <t>BMCOND</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Specimen Type</t>
+          <t>Target Condition or Exposure</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
@@ -3772,7 +3804,7 @@
       <c r="E80" s="6" t="inlineStr"/>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>The matrix the biomarker is measured in: SERUM, PLASMA, WHOLE BLOOD, URINE. Constant for the biomarker-assay, so it belongs to the claim rather than to a result. Decision thresholds do not transfer between matrices.</t>
+          <t>The disease or exposure the role is scoped to.</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr"/>
@@ -3786,9 +3818,9 @@
           <t>Proposed - not in SDTMIG v3.4</t>
         </is>
       </c>
-      <c r="J80" s="23" t="inlineStr">
-        <is>
-          <t>T</t>
+      <c r="J80" s="27" t="inlineStr">
+        <is>
+          <t>K</t>
         </is>
       </c>
     </row>
@@ -3798,25 +3830,25 @@
           <t>BM</t>
         </is>
       </c>
-      <c r="B81" s="28" t="inlineStr">
-        <is>
-          <t>BMSRCDOM</t>
+      <c r="B81" s="26" t="inlineStr">
+        <is>
+          <t>BMCONDID</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Source Domain</t>
+          <t>Condition Identifier</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>Identifier</t>
+          <t>Record Qualifier</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr"/>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>The SDTM domain holding the measurements this claim describes.</t>
+          <t>Ontology CURIE for the condition: DOID, MONDO.</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr"/>
@@ -3830,9 +3862,9 @@
           <t>Proposed - not in SDTMIG v3.4</t>
         </is>
       </c>
-      <c r="J81" s="29" t="inlineStr">
-        <is>
-          <t>N</t>
+      <c r="J81" s="27" t="inlineStr">
+        <is>
+          <t>K</t>
         </is>
       </c>
     </row>
@@ -3842,25 +3874,25 @@
           <t>BM</t>
         </is>
       </c>
-      <c r="B82" s="28" t="inlineStr">
-        <is>
-          <t>BMSRCVAR</t>
+      <c r="B82" s="22" t="inlineStr">
+        <is>
+          <t>BMASSAY</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Source Identifying Variable</t>
+          <t>Assay Profile Reference</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>Identifier</t>
+          <t>Record Qualifier</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr"/>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>The variable in that domain used to select the relevant records.</t>
+          <t>The assay the claim depends on. Decision thresholds are assay-specific and do not transfer between assays.</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr"/>
@@ -3874,9 +3906,9 @@
           <t>Proposed - not in SDTMIG v3.4</t>
         </is>
       </c>
-      <c r="J82" s="29" t="inlineStr">
-        <is>
-          <t>N</t>
+      <c r="J82" s="23" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -3886,25 +3918,25 @@
           <t>BM</t>
         </is>
       </c>
-      <c r="B83" s="28" t="inlineStr">
-        <is>
-          <t>BMSRCVAL</t>
+      <c r="B83" s="22" t="inlineStr">
+        <is>
+          <t>BMNAM</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Source Identifying Value</t>
+          <t>Assay Manufacturer</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>Identifier</t>
+          <t>Record Qualifier</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr"/>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>The value of BMSRCVAR that selects them.</t>
+          <t>Vendor of the assay named in BMASSAY.</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr"/>
@@ -3918,9 +3950,9 @@
           <t>Proposed - not in SDTMIG v3.4</t>
         </is>
       </c>
-      <c r="J83" s="29" t="inlineStr">
-        <is>
-          <t>N</t>
+      <c r="J83" s="23" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -3930,25 +3962,25 @@
           <t>BM</t>
         </is>
       </c>
-      <c r="B84" s="28" t="inlineStr">
-        <is>
-          <t>BMSRCVR2</t>
+      <c r="B84" s="22" t="inlineStr">
+        <is>
+          <t>BMPLAT</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>Source Identifying Variable 2</t>
+          <t>Assay Platform</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>Identifier</t>
+          <t>Record Qualifier</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr"/>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>A second variable used to narrow the selection. Needed when the first alone selects records from more than one assay.</t>
+          <t>Instrument the assay runs on.</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr"/>
@@ -3962,9 +3994,9 @@
           <t>Proposed - not in SDTMIG v3.4</t>
         </is>
       </c>
-      <c r="J84" s="29" t="inlineStr">
-        <is>
-          <t>N</t>
+      <c r="J84" s="23" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -3974,25 +4006,25 @@
           <t>BM</t>
         </is>
       </c>
-      <c r="B85" s="28" t="inlineStr">
-        <is>
-          <t>BMSRCVL2</t>
+      <c r="B85" s="22" t="inlineStr">
+        <is>
+          <t>BMMETHOD</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Source Identifying Value 2</t>
+          <t>Measurement Method</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>Identifier</t>
+          <t>Record Qualifier</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr"/>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>The value of BMSRCVR2 that narrows the selection.</t>
+          <t>The analytical technique, not the product: IMMUNOASSAY, MASS SPECTROMETRY, PCR. The product name is BMASSAY. Modelled on LBMETHOD, which carries the same distinction - putting a vendor assay name here is the commonest error.</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr"/>
@@ -4006,9 +4038,9 @@
           <t>Proposed - not in SDTMIG v3.4</t>
         </is>
       </c>
-      <c r="J85" s="29" t="inlineStr">
-        <is>
-          <t>N</t>
+      <c r="J85" s="23" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -4020,12 +4052,12 @@
       </c>
       <c r="B86" s="22" t="inlineStr">
         <is>
-          <t>BMBCOID</t>
+          <t>BMSPEC</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>BioCompute Object Identifier</t>
+          <t>Specimen Type</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
@@ -4036,7 +4068,7 @@
       <c r="E86" s="6" t="inlineStr"/>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>Identifier of the BioCompute Object (IEEE 2791-2020) holding the decision rule and assay specification as structured, versioned parameters. Authoritative; BMRULE is only its human-readable rendering.</t>
+          <t>The matrix the biomarker is measured in: SERUM, PLASMA, WHOLE BLOOD, URINE. Constant for the biomarker-assay, so it belongs to the claim rather than to a result. Decision thresholds do not transfer between matrices.</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr"/>
@@ -4062,25 +4094,25 @@
           <t>BM</t>
         </is>
       </c>
-      <c r="B87" s="22" t="inlineStr">
-        <is>
-          <t>BMRULE</t>
+      <c r="B87" s="28" t="inlineStr">
+        <is>
+          <t>BMSRCDOM</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>Interpretation or Decision Rule (text)</t>
+          <t>Source Domain</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>Record Qualifier</t>
+          <t>Identifier</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr"/>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>Human-readable rendering of the rule identified by BMBCOID. For reading, not for execution.</t>
+          <t>The SDTM domain holding the measurements this claim describes.</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr"/>
@@ -4094,9 +4126,9 @@
           <t>Proposed - not in SDTMIG v3.4</t>
         </is>
       </c>
-      <c r="J87" s="23" t="inlineStr">
-        <is>
-          <t>T</t>
+      <c r="J87" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -4106,25 +4138,25 @@
           <t>BM</t>
         </is>
       </c>
-      <c r="B88" s="26" t="inlineStr">
-        <is>
-          <t>BMEVID</t>
+      <c r="B88" s="28" t="inlineStr">
+        <is>
+          <t>BMSRCVAR</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Evidence Reference</t>
+          <t>Source Identifying Variable</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>Record Qualifier</t>
+          <t>Identifier</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr"/>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>Citation supporting the claim: PMID, DOI, internal report. Evidence only; who asserted it is BMASSRT.</t>
+          <t>The variable in that domain used to select the relevant records.</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr"/>
@@ -4138,9 +4170,9 @@
           <t>Proposed - not in SDTMIG v3.4</t>
         </is>
       </c>
-      <c r="J88" s="27" t="inlineStr">
-        <is>
-          <t>K</t>
+      <c r="J88" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -4152,23 +4184,23 @@
       </c>
       <c r="B89" s="28" t="inlineStr">
         <is>
-          <t>BMASSRT</t>
+          <t>BMSRCVAL</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Asserting Party</t>
+          <t>Source Identifying Value</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>Record Qualifier</t>
+          <t>Identifier</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr"/>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>Who asserted this biomarker context: sponsor, committee, regulator or consortium.</t>
+          <t>The value of BMSRCVAR that selects them.</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr"/>
@@ -4196,23 +4228,23 @@
       </c>
       <c r="B90" s="28" t="inlineStr">
         <is>
-          <t>BMASSDTC</t>
+          <t>BMSRCVR2</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>Assertion Date</t>
+          <t>Source Identifying Variable 2</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>Timing</t>
+          <t>Identifier</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr"/>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>When the claim at this BMVER was asserted, ISO 8601.</t>
+          <t>A second variable used to narrow the selection. Needed when the first alone selects records from more than one assay.</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr"/>
@@ -4233,37 +4265,33 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="19" t="inlineStr">
-        <is>
-          <t>SUPPLB QNAM</t>
-        </is>
-      </c>
-      <c r="B91" s="22" t="inlineStr">
-        <is>
-          <t>ASSAYNAM</t>
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>BM</t>
+        </is>
+      </c>
+      <c r="B91" s="28" t="inlineStr">
+        <is>
+          <t>BMSRCVL2</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>Assay Name</t>
+          <t>Source Identifying Value 2</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>Result Qualifier</t>
+          <t>Identifier</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr"/>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>Trade name of the assay used to produce the parent LB result.</t>
-        </is>
-      </c>
-      <c r="G91" s="5" t="inlineStr">
-        <is>
-          <t>Keyed on LBGRPID: one row per subject per assay, not one per result.</t>
-        </is>
-      </c>
+          <t>The value of BMSRCVR2 that narrows the selection.</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="inlineStr"/>
       <c r="H91" s="7" t="inlineStr">
         <is>
           <t>Proposed</t>
@@ -4274,44 +4302,40 @@
           <t>Proposed - not in SDTMIG v3.4</t>
         </is>
       </c>
-      <c r="J91" s="23" t="inlineStr">
-        <is>
-          <t>T</t>
+      <c r="J91" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>SUPPLB QNAM</t>
+          <t>BM</t>
         </is>
       </c>
       <c r="B92" s="22" t="inlineStr">
         <is>
-          <t>ASSAYPLT</t>
+          <t>BMBCOID</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>Assay Platform</t>
+          <t>BioCompute Object Identifier</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>Result Qualifier</t>
+          <t>Record Qualifier</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr"/>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>Instrument or analyser the assay was run on.</t>
-        </is>
-      </c>
-      <c r="G92" s="5" t="inlineStr">
-        <is>
-          <t>Keyed on LBGRPID.</t>
-        </is>
-      </c>
+          <t>Identifier of the BioCompute Object (IEEE 2791-2020) holding the decision rule and assay specification as structured, versioned parameters. Authoritative; BMRULE is only its human-readable rendering.</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="inlineStr"/>
       <c r="H92" s="7" t="inlineStr">
         <is>
           <t>Proposed</t>
@@ -4331,35 +4355,31 @@
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>SUPPLB QNAM</t>
+          <t>BM</t>
         </is>
       </c>
       <c r="B93" s="22" t="inlineStr">
         <is>
-          <t>LBLOD</t>
+          <t>BMRULE</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>Limit of Detection</t>
+          <t>Interpretation or Decision Rule (text)</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>Result Qualifier</t>
+          <t>Record Qualifier</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr"/>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>Lowest concentration distinguishable from a blank, per CLSI EP17.</t>
-        </is>
-      </c>
-      <c r="G93" s="5" t="inlineStr">
-        <is>
-          <t>Without it a censored result cannot be interpreted. Keyed on LBGRPID.</t>
-        </is>
-      </c>
+          <t>Human-readable rendering of the rule identified by BMBCOID. For reading, not for execution.</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr"/>
       <c r="H93" s="7" t="inlineStr">
         <is>
           <t>Proposed</t>
@@ -4379,35 +4399,31 @@
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>SUPPLB QNAM</t>
-        </is>
-      </c>
-      <c r="B94" s="22" t="inlineStr">
-        <is>
-          <t>LBLLOQ</t>
+          <t>BM</t>
+        </is>
+      </c>
+      <c r="B94" s="26" t="inlineStr">
+        <is>
+          <t>BMEVID</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>Lower Limit of Quantitation</t>
+          <t>Evidence Reference</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>Result Qualifier</t>
+          <t>Record Qualifier</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr"/>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>Lowest concentration measurable with stated precision, per CLSI EP17.</t>
-        </is>
-      </c>
-      <c r="G94" s="5" t="inlineStr">
-        <is>
-          <t>Values between LOD and LLOQ are detected but not quantifiable. Keyed on LBGRPID.</t>
-        </is>
-      </c>
+          <t>Citation supporting the claim: PMID, DOI, internal report. Evidence only; who asserted it is BMASSRT.</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="inlineStr"/>
       <c r="H94" s="7" t="inlineStr">
         <is>
           <t>Proposed</t>
@@ -4418,44 +4434,40 @@
           <t>Proposed - not in SDTMIG v3.4</t>
         </is>
       </c>
-      <c r="J94" s="23" t="inlineStr">
-        <is>
-          <t>T</t>
+      <c r="J94" s="27" t="inlineStr">
+        <is>
+          <t>K</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>SUPPLB QNAM</t>
-        </is>
-      </c>
-      <c r="B95" s="22" t="inlineStr">
-        <is>
-          <t>LBULOQ</t>
+          <t>BM</t>
+        </is>
+      </c>
+      <c r="B95" s="28" t="inlineStr">
+        <is>
+          <t>BMASSRT</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>Upper Limit of Quantitation</t>
+          <t>Asserting Party</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>Result Qualifier</t>
+          <t>Record Qualifier</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr"/>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>Highest concentration measurable without dilution.</t>
-        </is>
-      </c>
-      <c r="G95" s="5" t="inlineStr">
-        <is>
-          <t>Keyed on LBGRPID.</t>
-        </is>
-      </c>
+          <t>Who asserted this biomarker context: sponsor, committee, regulator or consortium.</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="inlineStr"/>
       <c r="H95" s="7" t="inlineStr">
         <is>
           <t>Proposed</t>
@@ -4466,44 +4478,40 @@
           <t>Proposed - not in SDTMIG v3.4</t>
         </is>
       </c>
-      <c r="J95" s="23" t="inlineStr">
-        <is>
-          <t>T</t>
+      <c r="J95" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>SUPPLB QNAM</t>
-        </is>
-      </c>
-      <c r="B96" s="24" t="inlineStr">
-        <is>
-          <t>CENSOR</t>
+          <t>BM</t>
+        </is>
+      </c>
+      <c r="B96" s="28" t="inlineStr">
+        <is>
+          <t>BMASSDTC</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>Censoring State</t>
+          <t>Assertion Date</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>Result Qualifier</t>
+          <t>Timing</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr"/>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>Which of the four measurement zones the result falls in: below_lod, detected_below_lloq, quantifiable, above_uloq.</t>
-        </is>
-      </c>
-      <c r="G96" s="5" t="inlineStr">
-        <is>
-          <t>Derived from the result against this run's limits, never entered by hand. The only qualifier keyed on LBSEQ, because it is the only one that varies per result.</t>
-        </is>
-      </c>
+          <t>When the claim at this BMVER was asserted, ISO 8601.</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="inlineStr"/>
       <c r="H96" s="7" t="inlineStr">
         <is>
           <t>Proposed</t>
@@ -4514,55 +4522,199 @@
           <t>Proposed - not in SDTMIG v3.4</t>
         </is>
       </c>
-      <c r="J96" s="25" t="inlineStr">
-        <is>
-          <t>R</t>
+      <c r="J96" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="6" t="inlineStr">
+      <c r="A97" s="19" t="inlineStr">
         <is>
           <t>SUPPLB QNAM</t>
         </is>
       </c>
-      <c r="B97" s="24" t="inlineStr">
-        <is>
-          <t>RBCOID</t>
+      <c r="B97" s="22" t="inlineStr">
+        <is>
+          <t>ASSAYNAM</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>Run BCO Identifier</t>
+          <t>Assay Name</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>Record Qualifier</t>
+          <t>Result Qualifier</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr"/>
       <c r="F97" s="5" t="inlineStr">
         <is>
+          <t>Trade name of the assay used to produce the parent LB result.</t>
+        </is>
+      </c>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>Keyed on LBGRPID: one row per subject per assay, not one per result.</t>
+        </is>
+      </c>
+      <c r="H97" s="7" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="I97" s="6" t="inlineStr">
+        <is>
+          <t>Proposed - not in SDTMIG v3.4</t>
+        </is>
+      </c>
+      <c r="J97" s="23" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>SUPPLB QNAM</t>
+        </is>
+      </c>
+      <c r="B98" s="22" t="inlineStr">
+        <is>
+          <t>ASSAYPLT</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>Assay Platform</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>Result Qualifier</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="inlineStr"/>
+      <c r="F98" s="5" t="inlineStr">
+        <is>
+          <t>Instrument or analyser the assay was run on.</t>
+        </is>
+      </c>
+      <c r="G98" s="5" t="inlineStr">
+        <is>
+          <t>Keyed on LBGRPID.</t>
+        </is>
+      </c>
+      <c r="H98" s="7" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="I98" s="6" t="inlineStr">
+        <is>
+          <t>Proposed - not in SDTMIG v3.4</t>
+        </is>
+      </c>
+      <c r="J98" s="23" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>SUPPLB QNAM</t>
+        </is>
+      </c>
+      <c r="B99" s="24" t="inlineStr">
+        <is>
+          <t>CENSOR</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>Censoring State</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>Result Qualifier</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr"/>
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>Which of the four measurement zones the result falls in: below_lod, detected_below_lloq, quantifiable, above_uloq.</t>
+        </is>
+      </c>
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>Derived from the result against this run's limits, never entered by hand. The only qualifier keyed on LBSEQ, because it is the only one that varies per result.</t>
+        </is>
+      </c>
+      <c r="H99" s="7" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="I99" s="6" t="inlineStr">
+        <is>
+          <t>Proposed - not in SDTMIG v3.4</t>
+        </is>
+      </c>
+      <c r="J99" s="25" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>SUPPLB QNAM</t>
+        </is>
+      </c>
+      <c r="B100" s="24" t="inlineStr">
+        <is>
+          <t>RBCOID</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>Run BCO Identifier</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>Record Qualifier</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="inlineStr"/>
+      <c r="F100" s="5" t="inlineStr">
+        <is>
           <t>object_id of the run BCO recording the analytical run that produced this result.</t>
         </is>
       </c>
-      <c r="G97" s="5" t="inlineStr">
+      <c r="G100" s="5" t="inlineStr">
         <is>
           <t>The only link from a result to its run; BM cannot carry it because BM has one row per biomarker, not per patient. Keyed on LBGRPID.</t>
         </is>
       </c>
-      <c r="H97" s="7" t="inlineStr">
+      <c r="H100" s="7" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="I97" s="6" t="inlineStr">
+      <c r="I100" s="6" t="inlineStr">
         <is>
           <t>Proposed - not in SDTMIG v3.4</t>
         </is>
       </c>
-      <c r="J97" s="25" t="inlineStr">
+      <c r="J100" s="25" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -4829,7 +4981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W10"/>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4847,20 +4999,26 @@
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
     <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="15" customWidth="1" min="18" max="18"/>
-    <col width="28" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="28" customWidth="1" min="21" max="21"/>
     <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="18" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="11" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="18" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>One row per lab test, per subject, per timepoint. Censored results carry the operator in LBORRES/LBSTRESC and leave LBSTRESN empty - standard SDTM practice.</t>
+          <t>One row per lab test, per subject, per timepoint. Results below the LoD carry the operator in LBORRES/LBSTRESC and leave LBSTRESN empty; results between the LoD and the LLOQ keep their numeric value and are flagged in SUPPLB.CENSOR. Assay limits are the standard variables LBLLOD, LBLLOQ and LBULOQ.</t>
         </is>
       </c>
     </row>
@@ -4922,60 +5080,90 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
+          <t>LBLLOD</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
           <t>LBSTRESC</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>LBSTRESN</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>LBSTRESU</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>LBSTNRLO</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>LBSTNRHI</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="R3" s="3" t="inlineStr">
         <is>
           <t>LBNRIND</t>
         </is>
       </c>
-      <c r="Q3" s="3" t="inlineStr">
+      <c r="S3" s="3" t="inlineStr">
         <is>
           <t>LBSPEC</t>
         </is>
       </c>
-      <c r="R3" s="3" t="inlineStr">
+      <c r="T3" s="3" t="inlineStr">
         <is>
           <t>LBMETHOD</t>
         </is>
       </c>
-      <c r="S3" s="3" t="inlineStr">
+      <c r="U3" s="3" t="inlineStr">
         <is>
           <t>LBNAM</t>
         </is>
       </c>
-      <c r="T3" s="3" t="inlineStr">
+      <c r="V3" s="3" t="inlineStr">
         <is>
           <t>LBLOINC</t>
         </is>
       </c>
-      <c r="U3" s="3" t="inlineStr">
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>LBLOBXFL</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>LBBLFL</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>LBLLOQ</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>LBULOQ</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>VISITNUM</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
         <is>
           <t>VISIT</t>
         </is>
       </c>
-      <c r="V3" s="3" t="inlineStr">
-        <is>
-          <t>LBBLFL</t>
-        </is>
-      </c>
-      <c r="W3" s="3" t="inlineStr">
+      <c r="AC3" s="3" t="inlineStr">
         <is>
           <t>LBDTC</t>
         </is>
@@ -5037,62 +5225,92 @@
           <t>T</t>
         </is>
       </c>
-      <c r="L4" s="30" t="inlineStr">
+      <c r="L4" s="32" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="M4" s="30" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="M4" s="30" t="inlineStr">
+      <c r="N4" s="30" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="N4" s="32" t="inlineStr">
+      <c r="O4" s="32" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="O4" s="32" t="inlineStr">
+      <c r="P4" s="32" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="P4" s="30" t="inlineStr">
+      <c r="Q4" s="32" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="R4" s="30" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="Q4" s="32" t="inlineStr">
+      <c r="S4" s="32" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="R4" s="32" t="inlineStr">
+      <c r="T4" s="32" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="S4" s="32" t="inlineStr">
+      <c r="U4" s="32" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="T4" s="32" t="inlineStr">
+      <c r="V4" s="32" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="U4" s="32" t="inlineStr">
+      <c r="W4" s="30" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="X4" s="30" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="Y4" s="32" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="V4" s="30" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="W4" s="33" t="inlineStr">
+      <c r="Z4" s="32" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AA4" s="32" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AB4" s="32" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AC4" s="33" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -5129,12 +5347,12 @@
       </c>
       <c r="G5" s="31" t="inlineStr">
         <is>
-          <t>TNNI3</t>
+          <t>TROPONI3</t>
         </is>
       </c>
       <c r="H5" s="31" t="inlineStr">
         <is>
-          <t>Troponin I, Cardiac Muscle</t>
+          <t>Troponin I Type 3</t>
         </is>
       </c>
       <c r="I5" s="31" t="inlineStr">
@@ -5152,58 +5370,74 @@
           <t>ng/mL</t>
         </is>
       </c>
-      <c r="L5" s="34" t="inlineStr">
+      <c r="L5" s="31" t="inlineStr">
+        <is>
+          <t>0.006</t>
+        </is>
+      </c>
+      <c r="M5" s="34" t="inlineStr">
         <is>
           <t>0.021</t>
         </is>
       </c>
-      <c r="M5" s="34" t="n">
+      <c r="N5" s="34" t="n">
         <v>0.021</v>
       </c>
-      <c r="N5" s="31" t="inlineStr">
+      <c r="O5" s="31" t="inlineStr">
         <is>
           <t>ng/mL</t>
         </is>
       </c>
-      <c r="O5" s="31" t="n">
+      <c r="P5" s="31" t="n"/>
+      <c r="Q5" s="31" t="n">
         <v>0.04</v>
       </c>
-      <c r="P5" s="31" t="inlineStr">
+      <c r="R5" s="31" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="Q5" s="31" t="inlineStr">
+      <c r="S5" s="31" t="inlineStr">
         <is>
           <t>SERUM</t>
         </is>
       </c>
-      <c r="R5" s="31" t="inlineStr">
+      <c r="T5" s="31" t="inlineStr">
         <is>
           <t>IMMUNOASSAY</t>
         </is>
       </c>
-      <c r="S5" s="31" t="inlineStr">
+      <c r="U5" s="31" t="inlineStr">
         <is>
           <t>Siemens Healthcare Diagnostics</t>
         </is>
       </c>
-      <c r="T5" s="31" t="inlineStr">
+      <c r="V5" s="31" t="inlineStr">
         <is>
           <t>10839-9</t>
         </is>
       </c>
-      <c r="U5" s="31" t="inlineStr">
+      <c r="W5" s="31" t="n"/>
+      <c r="X5" s="31" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Y5" s="31" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Z5" s="31" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA5" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="31" t="inlineStr">
         <is>
           <t>ADMISSION</t>
         </is>
       </c>
-      <c r="V5" s="31" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="W5" s="31" t="inlineStr">
+      <c r="AC5" s="31" t="inlineStr">
         <is>
           <t>2026-03-15T08:10</t>
         </is>
@@ -5240,12 +5474,12 @@
       </c>
       <c r="G6" s="31" t="inlineStr">
         <is>
-          <t>TNNI3</t>
+          <t>TROPONI3</t>
         </is>
       </c>
       <c r="H6" s="31" t="inlineStr">
         <is>
-          <t>Troponin I, Cardiac Muscle</t>
+          <t>Troponin I Type 3</t>
         </is>
       </c>
       <c r="I6" s="31" t="inlineStr">
@@ -5263,58 +5497,70 @@
           <t>ng/mL</t>
         </is>
       </c>
-      <c r="L6" s="34" t="inlineStr">
+      <c r="L6" s="31" t="inlineStr">
+        <is>
+          <t>0.006</t>
+        </is>
+      </c>
+      <c r="M6" s="34" t="inlineStr">
         <is>
           <t>0.058</t>
         </is>
       </c>
-      <c r="M6" s="34" t="n">
+      <c r="N6" s="34" t="n">
         <v>0.058</v>
       </c>
-      <c r="N6" s="31" t="inlineStr">
+      <c r="O6" s="31" t="inlineStr">
         <is>
           <t>ng/mL</t>
         </is>
       </c>
-      <c r="O6" s="31" t="n">
+      <c r="P6" s="31" t="n"/>
+      <c r="Q6" s="31" t="n">
         <v>0.04</v>
       </c>
-      <c r="P6" s="31" t="inlineStr">
+      <c r="R6" s="31" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="Q6" s="31" t="inlineStr">
+      <c r="S6" s="31" t="inlineStr">
         <is>
           <t>SERUM</t>
         </is>
       </c>
-      <c r="R6" s="31" t="inlineStr">
+      <c r="T6" s="31" t="inlineStr">
         <is>
           <t>IMMUNOASSAY</t>
         </is>
       </c>
-      <c r="S6" s="31" t="inlineStr">
+      <c r="U6" s="31" t="inlineStr">
         <is>
           <t>Siemens Healthcare Diagnostics</t>
         </is>
       </c>
-      <c r="T6" s="31" t="inlineStr">
+      <c r="V6" s="31" t="inlineStr">
         <is>
           <t>10839-9</t>
         </is>
       </c>
-      <c r="U6" s="31" t="inlineStr">
+      <c r="W6" s="31" t="n"/>
+      <c r="X6" s="31" t="n"/>
+      <c r="Y6" s="31" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Z6" s="31" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA6" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB6" s="31" t="inlineStr">
         <is>
           <t>3 HOURS</t>
         </is>
       </c>
-      <c r="V6" s="31" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="W6" s="31" t="inlineStr">
+      <c r="AC6" s="31" t="inlineStr">
         <is>
           <t>2026-03-15T11:10</t>
         </is>
@@ -5351,12 +5597,12 @@
       </c>
       <c r="G7" s="31" t="inlineStr">
         <is>
-          <t>TNNI3</t>
+          <t>TROPONI3</t>
         </is>
       </c>
       <c r="H7" s="31" t="inlineStr">
         <is>
-          <t>Troponin I, Cardiac Muscle</t>
+          <t>Troponin I Type 3</t>
         </is>
       </c>
       <c r="I7" s="31" t="inlineStr">
@@ -5374,58 +5620,70 @@
           <t>ng/mL</t>
         </is>
       </c>
-      <c r="L7" s="34" t="inlineStr">
+      <c r="L7" s="31" t="inlineStr">
+        <is>
+          <t>0.006</t>
+        </is>
+      </c>
+      <c r="M7" s="34" t="inlineStr">
         <is>
           <t>0.094</t>
         </is>
       </c>
-      <c r="M7" s="34" t="n">
+      <c r="N7" s="34" t="n">
         <v>0.094</v>
       </c>
-      <c r="N7" s="31" t="inlineStr">
+      <c r="O7" s="31" t="inlineStr">
         <is>
           <t>ng/mL</t>
         </is>
       </c>
-      <c r="O7" s="31" t="n">
+      <c r="P7" s="31" t="n"/>
+      <c r="Q7" s="31" t="n">
         <v>0.04</v>
       </c>
-      <c r="P7" s="31" t="inlineStr">
+      <c r="R7" s="31" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="Q7" s="31" t="inlineStr">
+      <c r="S7" s="31" t="inlineStr">
         <is>
           <t>SERUM</t>
         </is>
       </c>
-      <c r="R7" s="31" t="inlineStr">
+      <c r="T7" s="31" t="inlineStr">
         <is>
           <t>IMMUNOASSAY</t>
         </is>
       </c>
-      <c r="S7" s="31" t="inlineStr">
+      <c r="U7" s="31" t="inlineStr">
         <is>
           <t>Siemens Healthcare Diagnostics</t>
         </is>
       </c>
-      <c r="T7" s="31" t="inlineStr">
+      <c r="V7" s="31" t="inlineStr">
         <is>
           <t>10839-9</t>
         </is>
       </c>
-      <c r="U7" s="31" t="inlineStr">
+      <c r="W7" s="31" t="n"/>
+      <c r="X7" s="31" t="n"/>
+      <c r="Y7" s="31" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Z7" s="31" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA7" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB7" s="31" t="inlineStr">
         <is>
           <t>6 HOURS</t>
         </is>
       </c>
-      <c r="V7" s="31" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="W7" s="31" t="inlineStr">
+      <c r="AC7" s="31" t="inlineStr">
         <is>
           <t>2026-03-15T14:10</t>
         </is>
@@ -5462,12 +5720,12 @@
       </c>
       <c r="G8" s="31" t="inlineStr">
         <is>
-          <t>TNNI3</t>
+          <t>TROPONI3</t>
         </is>
       </c>
       <c r="H8" s="31" t="inlineStr">
         <is>
-          <t>Troponin I, Cardiac Muscle</t>
+          <t>Troponin I Type 3</t>
         </is>
       </c>
       <c r="I8" s="31" t="inlineStr">
@@ -5485,56 +5743,72 @@
           <t>ng/mL</t>
         </is>
       </c>
-      <c r="L8" s="34" t="inlineStr">
+      <c r="L8" s="31" t="inlineStr">
+        <is>
+          <t>0.006</t>
+        </is>
+      </c>
+      <c r="M8" s="34" t="inlineStr">
         <is>
           <t>&lt;0.006</t>
         </is>
       </c>
-      <c r="M8" s="34" t="n"/>
-      <c r="N8" s="31" t="inlineStr">
+      <c r="N8" s="34" t="n"/>
+      <c r="O8" s="31" t="inlineStr">
         <is>
           <t>ng/mL</t>
         </is>
       </c>
-      <c r="O8" s="31" t="n">
+      <c r="P8" s="31" t="n"/>
+      <c r="Q8" s="31" t="n">
         <v>0.04</v>
       </c>
-      <c r="P8" s="31" t="inlineStr">
+      <c r="R8" s="31" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="Q8" s="31" t="inlineStr">
+      <c r="S8" s="31" t="inlineStr">
         <is>
           <t>SERUM</t>
         </is>
       </c>
-      <c r="R8" s="31" t="inlineStr">
+      <c r="T8" s="31" t="inlineStr">
         <is>
           <t>IMMUNOASSAY</t>
         </is>
       </c>
-      <c r="S8" s="31" t="inlineStr">
+      <c r="U8" s="31" t="inlineStr">
         <is>
           <t>Siemens Healthcare Diagnostics</t>
         </is>
       </c>
-      <c r="T8" s="31" t="inlineStr">
+      <c r="V8" s="31" t="inlineStr">
         <is>
           <t>10839-9</t>
         </is>
       </c>
-      <c r="U8" s="31" t="inlineStr">
+      <c r="W8" s="31" t="n"/>
+      <c r="X8" s="31" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Y8" s="31" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Z8" s="31" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA8" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB8" s="31" t="inlineStr">
         <is>
           <t>ADMISSION</t>
         </is>
       </c>
-      <c r="V8" s="31" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="W8" s="31" t="inlineStr">
+      <c r="AC8" s="31" t="inlineStr">
         <is>
           <t>2026-03-16T13:55</t>
         </is>
@@ -5571,12 +5845,12 @@
       </c>
       <c r="G9" s="31" t="inlineStr">
         <is>
-          <t>TNNI3</t>
+          <t>TROPONI3</t>
         </is>
       </c>
       <c r="H9" s="31" t="inlineStr">
         <is>
-          <t>Troponin I, Cardiac Muscle</t>
+          <t>Troponin I Type 3</t>
         </is>
       </c>
       <c r="I9" s="31" t="inlineStr">
@@ -5594,58 +5868,70 @@
           <t>ng/mL</t>
         </is>
       </c>
-      <c r="L9" s="34" t="inlineStr">
+      <c r="L9" s="31" t="inlineStr">
+        <is>
+          <t>0.006</t>
+        </is>
+      </c>
+      <c r="M9" s="34" t="inlineStr">
         <is>
           <t>0.008</t>
         </is>
       </c>
-      <c r="M9" s="34" t="n">
+      <c r="N9" s="34" t="n">
         <v>0.008</v>
       </c>
-      <c r="N9" s="31" t="inlineStr">
+      <c r="O9" s="31" t="inlineStr">
         <is>
           <t>ng/mL</t>
         </is>
       </c>
-      <c r="O9" s="31" t="n">
+      <c r="P9" s="31" t="n"/>
+      <c r="Q9" s="31" t="n">
         <v>0.04</v>
       </c>
-      <c r="P9" s="31" t="inlineStr">
+      <c r="R9" s="31" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="Q9" s="31" t="inlineStr">
+      <c r="S9" s="31" t="inlineStr">
         <is>
           <t>SERUM</t>
         </is>
       </c>
-      <c r="R9" s="31" t="inlineStr">
+      <c r="T9" s="31" t="inlineStr">
         <is>
           <t>IMMUNOASSAY</t>
         </is>
       </c>
-      <c r="S9" s="31" t="inlineStr">
+      <c r="U9" s="31" t="inlineStr">
         <is>
           <t>Siemens Healthcare Diagnostics</t>
         </is>
       </c>
-      <c r="T9" s="31" t="inlineStr">
+      <c r="V9" s="31" t="inlineStr">
         <is>
           <t>10839-9</t>
         </is>
       </c>
-      <c r="U9" s="31" t="inlineStr">
+      <c r="W9" s="31" t="n"/>
+      <c r="X9" s="31" t="n"/>
+      <c r="Y9" s="31" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Z9" s="31" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA9" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB9" s="31" t="inlineStr">
         <is>
           <t>3 HOURS</t>
         </is>
       </c>
-      <c r="V9" s="31" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="W9" s="31" t="inlineStr">
+      <c r="AC9" s="31" t="inlineStr">
         <is>
           <t>2026-03-16T16:55</t>
         </is>
@@ -5682,12 +5968,12 @@
       </c>
       <c r="G10" s="31" t="inlineStr">
         <is>
-          <t>TNNI3</t>
+          <t>TROPONI3</t>
         </is>
       </c>
       <c r="H10" s="31" t="inlineStr">
         <is>
-          <t>Troponin I, Cardiac Muscle</t>
+          <t>Troponin I Type 3</t>
         </is>
       </c>
       <c r="I10" s="31" t="inlineStr">
@@ -5705,58 +5991,70 @@
           <t>ng/mL</t>
         </is>
       </c>
-      <c r="L10" s="34" t="inlineStr">
+      <c r="L10" s="31" t="inlineStr">
+        <is>
+          <t>0.006</t>
+        </is>
+      </c>
+      <c r="M10" s="34" t="inlineStr">
         <is>
           <t>0.045</t>
         </is>
       </c>
-      <c r="M10" s="34" t="n">
+      <c r="N10" s="34" t="n">
         <v>0.045</v>
       </c>
-      <c r="N10" s="31" t="inlineStr">
+      <c r="O10" s="31" t="inlineStr">
         <is>
           <t>ng/mL</t>
         </is>
       </c>
-      <c r="O10" s="31" t="n">
+      <c r="P10" s="31" t="n"/>
+      <c r="Q10" s="31" t="n">
         <v>0.04</v>
       </c>
-      <c r="P10" s="31" t="inlineStr">
+      <c r="R10" s="31" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="Q10" s="31" t="inlineStr">
+      <c r="S10" s="31" t="inlineStr">
         <is>
           <t>SERUM</t>
         </is>
       </c>
-      <c r="R10" s="31" t="inlineStr">
+      <c r="T10" s="31" t="inlineStr">
         <is>
           <t>IMMUNOASSAY</t>
         </is>
       </c>
-      <c r="S10" s="31" t="inlineStr">
+      <c r="U10" s="31" t="inlineStr">
         <is>
           <t>Siemens Healthcare Diagnostics</t>
         </is>
       </c>
-      <c r="T10" s="31" t="inlineStr">
+      <c r="V10" s="31" t="inlineStr">
         <is>
           <t>10839-9</t>
         </is>
       </c>
-      <c r="U10" s="31" t="inlineStr">
+      <c r="W10" s="31" t="n"/>
+      <c r="X10" s="31" t="n"/>
+      <c r="Y10" s="31" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Z10" s="31" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA10" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB10" s="31" t="inlineStr">
         <is>
           <t>6 HOURS</t>
         </is>
       </c>
-      <c r="V10" s="31" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="W10" s="31" t="inlineStr">
+      <c r="AC10" s="31" t="inlineStr">
         <is>
           <t>2026-03-16T19:55</t>
         </is>
@@ -5773,7 +6071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5791,7 +6089,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Supplemental qualifiers. QNAM names the fact, QVAL carries it, IDVAR/IDVARVAL point back at the LB record(s). Assay-level facts are keyed on LBGRPID so one row covers a whole block of results; only CENSOR is keyed on LBSEQ. The colour is on QNAM because provenance varies by row, not by column.</t>
+          <t>Supplemental qualifiers. QNAM names the fact, QVAL carries it, IDVAR/IDVARVAL point back at the LB record(s). Assay-level facts (ASSAYNAM, ASSAYPLT, RBCOID) are keyed on LBGRPID so one row covers a whole block of results; only CENSOR is keyed on LBSEQ. Assay limits moved to LB (LBLLOD/LBLLOQ/LBULOQ), as SDTMIG v3.4 §8.4.4 requires. The colour is on QNAM because provenance varies by row, not by column.</t>
         </is>
       </c>
     </row>
@@ -5977,18 +6275,20 @@
           <t>TNIULTRA</t>
         </is>
       </c>
-      <c r="F6" s="35" t="inlineStr">
-        <is>
-          <t>LBLOD</t>
+      <c r="F6" s="36" t="inlineStr">
+        <is>
+          <t>RBCOID</t>
         </is>
       </c>
       <c r="G6" s="31" t="inlineStr">
         <is>
-          <t>Limit of Detection</t>
-        </is>
-      </c>
-      <c r="H6" s="31" t="n">
-        <v>0.006</v>
+          <t>Run BCO Identifier</t>
+        </is>
+      </c>
+      <c r="H6" s="31" t="inlineStr">
+        <is>
+          <t>https://biocomputeobject.org/PLACEHOLDER_Troponin_I_patient1_rBCO/1.0.0</t>
+        </is>
       </c>
       <c r="I6" s="31" t="inlineStr">
         <is>
@@ -5997,7 +6297,7 @@
       </c>
       <c r="J6" s="31" t="inlineStr">
         <is>
-          <t>VENDOR</t>
+          <t>SPONSOR</t>
         </is>
       </c>
     </row>
@@ -6019,35 +6319,35 @@
       </c>
       <c r="D7" s="31" t="inlineStr">
         <is>
-          <t>LBGRPID</t>
-        </is>
-      </c>
-      <c r="E7" s="31" t="inlineStr">
-        <is>
-          <t>TNIULTRA</t>
-        </is>
-      </c>
-      <c r="F7" s="35" t="inlineStr">
-        <is>
-          <t>LBLLOQ</t>
+          <t>LBSEQ</t>
+        </is>
+      </c>
+      <c r="E7" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="36" t="inlineStr">
+        <is>
+          <t>CENSOR</t>
         </is>
       </c>
       <c r="G7" s="31" t="inlineStr">
         <is>
-          <t>Lower Limit of Quantitation</t>
-        </is>
-      </c>
-      <c r="H7" s="31" t="n">
-        <v>0.03</v>
+          <t>Censoring State</t>
+        </is>
+      </c>
+      <c r="H7" s="31" t="inlineStr">
+        <is>
+          <t>detected_below_lloq</t>
+        </is>
       </c>
       <c r="I7" s="31" t="inlineStr">
         <is>
-          <t>Assigned</t>
+          <t>Derived</t>
         </is>
       </c>
       <c r="J7" s="31" t="inlineStr">
         <is>
-          <t>VENDOR</t>
+          <t>SPONSOR</t>
         </is>
       </c>
     </row>
@@ -6069,35 +6369,35 @@
       </c>
       <c r="D8" s="31" t="inlineStr">
         <is>
-          <t>LBGRPID</t>
-        </is>
-      </c>
-      <c r="E8" s="31" t="inlineStr">
-        <is>
-          <t>TNIULTRA</t>
-        </is>
-      </c>
-      <c r="F8" s="35" t="inlineStr">
-        <is>
-          <t>LBULOQ</t>
+          <t>LBSEQ</t>
+        </is>
+      </c>
+      <c r="E8" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="36" t="inlineStr">
+        <is>
+          <t>CENSOR</t>
         </is>
       </c>
       <c r="G8" s="31" t="inlineStr">
         <is>
-          <t>Upper Limit of Quantitation</t>
-        </is>
-      </c>
-      <c r="H8" s="31" t="n">
-        <v>50</v>
+          <t>Censoring State</t>
+        </is>
+      </c>
+      <c r="H8" s="31" t="inlineStr">
+        <is>
+          <t>quantifiable</t>
+        </is>
       </c>
       <c r="I8" s="31" t="inlineStr">
         <is>
-          <t>Assigned</t>
+          <t>Derived</t>
         </is>
       </c>
       <c r="J8" s="31" t="inlineStr">
         <is>
-          <t>VENDOR</t>
+          <t>SPONSOR</t>
         </is>
       </c>
     </row>
@@ -6119,32 +6419,30 @@
       </c>
       <c r="D9" s="31" t="inlineStr">
         <is>
-          <t>LBGRPID</t>
-        </is>
-      </c>
-      <c r="E9" s="31" t="inlineStr">
-        <is>
-          <t>TNIULTRA</t>
-        </is>
+          <t>LBSEQ</t>
+        </is>
+      </c>
+      <c r="E9" s="31" t="n">
+        <v>3</v>
       </c>
       <c r="F9" s="36" t="inlineStr">
         <is>
-          <t>RBCOID</t>
+          <t>CENSOR</t>
         </is>
       </c>
       <c r="G9" s="31" t="inlineStr">
         <is>
-          <t>Run BCO Identifier</t>
+          <t>Censoring State</t>
         </is>
       </c>
       <c r="H9" s="31" t="inlineStr">
         <is>
-          <t>https://biocomputeobject.org/PLACEHOLDER_Troponin_I_patient1_rBCO/1.0.0</t>
+          <t>quantifiable</t>
         </is>
       </c>
       <c r="I9" s="31" t="inlineStr">
         <is>
-          <t>Assigned</t>
+          <t>Derived</t>
         </is>
       </c>
       <c r="J9" s="31" t="inlineStr">
@@ -6166,40 +6464,42 @@
       </c>
       <c r="C10" s="31" t="inlineStr">
         <is>
-          <t>BM-2026-01-001</t>
+          <t>BM-2026-01-002</t>
         </is>
       </c>
       <c r="D10" s="31" t="inlineStr">
         <is>
-          <t>LBSEQ</t>
-        </is>
-      </c>
-      <c r="E10" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="36" t="inlineStr">
-        <is>
-          <t>CENSOR</t>
+          <t>LBGRPID</t>
+        </is>
+      </c>
+      <c r="E10" s="31" t="inlineStr">
+        <is>
+          <t>TNIULTRA</t>
+        </is>
+      </c>
+      <c r="F10" s="35" t="inlineStr">
+        <is>
+          <t>ASSAYNAM</t>
         </is>
       </c>
       <c r="G10" s="31" t="inlineStr">
         <is>
-          <t>Censoring State</t>
+          <t>Assay Name</t>
         </is>
       </c>
       <c r="H10" s="31" t="inlineStr">
         <is>
-          <t>detected_below_lloq</t>
+          <t>TnI-Ultra</t>
         </is>
       </c>
       <c r="I10" s="31" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>Assigned</t>
         </is>
       </c>
       <c r="J10" s="31" t="inlineStr">
         <is>
-          <t>SPONSOR</t>
+          <t>VENDOR</t>
         </is>
       </c>
     </row>
@@ -6216,40 +6516,42 @@
       </c>
       <c r="C11" s="31" t="inlineStr">
         <is>
-          <t>BM-2026-01-001</t>
+          <t>BM-2026-01-002</t>
         </is>
       </c>
       <c r="D11" s="31" t="inlineStr">
         <is>
-          <t>LBSEQ</t>
-        </is>
-      </c>
-      <c r="E11" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="F11" s="36" t="inlineStr">
-        <is>
-          <t>CENSOR</t>
+          <t>LBGRPID</t>
+        </is>
+      </c>
+      <c r="E11" s="31" t="inlineStr">
+        <is>
+          <t>TNIULTRA</t>
+        </is>
+      </c>
+      <c r="F11" s="35" t="inlineStr">
+        <is>
+          <t>ASSAYPLT</t>
         </is>
       </c>
       <c r="G11" s="31" t="inlineStr">
         <is>
-          <t>Censoring State</t>
+          <t>Assay Platform</t>
         </is>
       </c>
       <c r="H11" s="31" t="inlineStr">
         <is>
-          <t>quantifiable</t>
+          <t>ADVIA Centaur XP</t>
         </is>
       </c>
       <c r="I11" s="31" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>Assigned</t>
         </is>
       </c>
       <c r="J11" s="31" t="inlineStr">
         <is>
-          <t>SPONSOR</t>
+          <t>VENDOR</t>
         </is>
       </c>
     </row>
@@ -6266,35 +6568,37 @@
       </c>
       <c r="C12" s="31" t="inlineStr">
         <is>
-          <t>BM-2026-01-001</t>
+          <t>BM-2026-01-002</t>
         </is>
       </c>
       <c r="D12" s="31" t="inlineStr">
         <is>
-          <t>LBSEQ</t>
-        </is>
-      </c>
-      <c r="E12" s="31" t="n">
-        <v>3</v>
+          <t>LBGRPID</t>
+        </is>
+      </c>
+      <c r="E12" s="31" t="inlineStr">
+        <is>
+          <t>TNIULTRA</t>
+        </is>
       </c>
       <c r="F12" s="36" t="inlineStr">
         <is>
-          <t>CENSOR</t>
+          <t>RBCOID</t>
         </is>
       </c>
       <c r="G12" s="31" t="inlineStr">
         <is>
-          <t>Censoring State</t>
+          <t>Run BCO Identifier</t>
         </is>
       </c>
       <c r="H12" s="31" t="inlineStr">
         <is>
-          <t>quantifiable</t>
+          <t>https://biocomputeobject.org/PLACEHOLDER_Troponin_I_patient2_rBCO/1.0.0</t>
         </is>
       </c>
       <c r="I12" s="31" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>Assigned</t>
         </is>
       </c>
       <c r="J12" s="31" t="inlineStr">
@@ -6321,37 +6625,35 @@
       </c>
       <c r="D13" s="31" t="inlineStr">
         <is>
-          <t>LBGRPID</t>
-        </is>
-      </c>
-      <c r="E13" s="31" t="inlineStr">
-        <is>
-          <t>TNIULTRA</t>
-        </is>
-      </c>
-      <c r="F13" s="35" t="inlineStr">
-        <is>
-          <t>ASSAYNAM</t>
+          <t>LBSEQ</t>
+        </is>
+      </c>
+      <c r="E13" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="36" t="inlineStr">
+        <is>
+          <t>CENSOR</t>
         </is>
       </c>
       <c r="G13" s="31" t="inlineStr">
         <is>
-          <t>Assay Name</t>
+          <t>Censoring State</t>
         </is>
       </c>
       <c r="H13" s="31" t="inlineStr">
         <is>
-          <t>TnI-Ultra</t>
+          <t>below_lod</t>
         </is>
       </c>
       <c r="I13" s="31" t="inlineStr">
         <is>
-          <t>Assigned</t>
+          <t>Derived</t>
         </is>
       </c>
       <c r="J13" s="31" t="inlineStr">
         <is>
-          <t>VENDOR</t>
+          <t>SPONSOR</t>
         </is>
       </c>
     </row>
@@ -6373,37 +6675,35 @@
       </c>
       <c r="D14" s="31" t="inlineStr">
         <is>
-          <t>LBGRPID</t>
-        </is>
-      </c>
-      <c r="E14" s="31" t="inlineStr">
-        <is>
-          <t>TNIULTRA</t>
-        </is>
-      </c>
-      <c r="F14" s="35" t="inlineStr">
-        <is>
-          <t>ASSAYPLT</t>
+          <t>LBSEQ</t>
+        </is>
+      </c>
+      <c r="E14" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="36" t="inlineStr">
+        <is>
+          <t>CENSOR</t>
         </is>
       </c>
       <c r="G14" s="31" t="inlineStr">
         <is>
-          <t>Assay Platform</t>
+          <t>Censoring State</t>
         </is>
       </c>
       <c r="H14" s="31" t="inlineStr">
         <is>
-          <t>ADVIA Centaur XP</t>
+          <t>detected_below_lloq</t>
         </is>
       </c>
       <c r="I14" s="31" t="inlineStr">
         <is>
-          <t>Assigned</t>
+          <t>Derived</t>
         </is>
       </c>
       <c r="J14" s="31" t="inlineStr">
         <is>
-          <t>VENDOR</t>
+          <t>SPONSOR</t>
         </is>
       </c>
     </row>
@@ -6425,335 +6725,33 @@
       </c>
       <c r="D15" s="31" t="inlineStr">
         <is>
-          <t>LBGRPID</t>
-        </is>
-      </c>
-      <c r="E15" s="31" t="inlineStr">
-        <is>
-          <t>TNIULTRA</t>
-        </is>
-      </c>
-      <c r="F15" s="35" t="inlineStr">
-        <is>
-          <t>LBLOD</t>
+          <t>LBSEQ</t>
+        </is>
+      </c>
+      <c r="E15" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" s="36" t="inlineStr">
+        <is>
+          <t>CENSOR</t>
         </is>
       </c>
       <c r="G15" s="31" t="inlineStr">
         <is>
-          <t>Limit of Detection</t>
-        </is>
-      </c>
-      <c r="H15" s="31" t="n">
-        <v>0.006</v>
+          <t>Censoring State</t>
+        </is>
+      </c>
+      <c r="H15" s="31" t="inlineStr">
+        <is>
+          <t>quantifiable</t>
+        </is>
       </c>
       <c r="I15" s="31" t="inlineStr">
         <is>
-          <t>Assigned</t>
+          <t>Derived</t>
         </is>
       </c>
       <c r="J15" s="31" t="inlineStr">
-        <is>
-          <t>VENDOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="31" t="inlineStr">
-        <is>
-          <t>BM-2026-01</t>
-        </is>
-      </c>
-      <c r="B16" s="31" t="inlineStr">
-        <is>
-          <t>LB</t>
-        </is>
-      </c>
-      <c r="C16" s="31" t="inlineStr">
-        <is>
-          <t>BM-2026-01-002</t>
-        </is>
-      </c>
-      <c r="D16" s="31" t="inlineStr">
-        <is>
-          <t>LBGRPID</t>
-        </is>
-      </c>
-      <c r="E16" s="31" t="inlineStr">
-        <is>
-          <t>TNIULTRA</t>
-        </is>
-      </c>
-      <c r="F16" s="35" t="inlineStr">
-        <is>
-          <t>LBLLOQ</t>
-        </is>
-      </c>
-      <c r="G16" s="31" t="inlineStr">
-        <is>
-          <t>Lower Limit of Quantitation</t>
-        </is>
-      </c>
-      <c r="H16" s="31" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I16" s="31" t="inlineStr">
-        <is>
-          <t>Assigned</t>
-        </is>
-      </c>
-      <c r="J16" s="31" t="inlineStr">
-        <is>
-          <t>VENDOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="31" t="inlineStr">
-        <is>
-          <t>BM-2026-01</t>
-        </is>
-      </c>
-      <c r="B17" s="31" t="inlineStr">
-        <is>
-          <t>LB</t>
-        </is>
-      </c>
-      <c r="C17" s="31" t="inlineStr">
-        <is>
-          <t>BM-2026-01-002</t>
-        </is>
-      </c>
-      <c r="D17" s="31" t="inlineStr">
-        <is>
-          <t>LBGRPID</t>
-        </is>
-      </c>
-      <c r="E17" s="31" t="inlineStr">
-        <is>
-          <t>TNIULTRA</t>
-        </is>
-      </c>
-      <c r="F17" s="35" t="inlineStr">
-        <is>
-          <t>LBULOQ</t>
-        </is>
-      </c>
-      <c r="G17" s="31" t="inlineStr">
-        <is>
-          <t>Upper Limit of Quantitation</t>
-        </is>
-      </c>
-      <c r="H17" s="31" t="n">
-        <v>50</v>
-      </c>
-      <c r="I17" s="31" t="inlineStr">
-        <is>
-          <t>Assigned</t>
-        </is>
-      </c>
-      <c r="J17" s="31" t="inlineStr">
-        <is>
-          <t>VENDOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="31" t="inlineStr">
-        <is>
-          <t>BM-2026-01</t>
-        </is>
-      </c>
-      <c r="B18" s="31" t="inlineStr">
-        <is>
-          <t>LB</t>
-        </is>
-      </c>
-      <c r="C18" s="31" t="inlineStr">
-        <is>
-          <t>BM-2026-01-002</t>
-        </is>
-      </c>
-      <c r="D18" s="31" t="inlineStr">
-        <is>
-          <t>LBGRPID</t>
-        </is>
-      </c>
-      <c r="E18" s="31" t="inlineStr">
-        <is>
-          <t>TNIULTRA</t>
-        </is>
-      </c>
-      <c r="F18" s="36" t="inlineStr">
-        <is>
-          <t>RBCOID</t>
-        </is>
-      </c>
-      <c r="G18" s="31" t="inlineStr">
-        <is>
-          <t>Run BCO Identifier</t>
-        </is>
-      </c>
-      <c r="H18" s="31" t="inlineStr">
-        <is>
-          <t>https://biocomputeobject.org/PLACEHOLDER_Troponin_I_patient2_rBCO/1.0.0</t>
-        </is>
-      </c>
-      <c r="I18" s="31" t="inlineStr">
-        <is>
-          <t>Assigned</t>
-        </is>
-      </c>
-      <c r="J18" s="31" t="inlineStr">
-        <is>
-          <t>SPONSOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="31" t="inlineStr">
-        <is>
-          <t>BM-2026-01</t>
-        </is>
-      </c>
-      <c r="B19" s="31" t="inlineStr">
-        <is>
-          <t>LB</t>
-        </is>
-      </c>
-      <c r="C19" s="31" t="inlineStr">
-        <is>
-          <t>BM-2026-01-002</t>
-        </is>
-      </c>
-      <c r="D19" s="31" t="inlineStr">
-        <is>
-          <t>LBSEQ</t>
-        </is>
-      </c>
-      <c r="E19" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="36" t="inlineStr">
-        <is>
-          <t>CENSOR</t>
-        </is>
-      </c>
-      <c r="G19" s="31" t="inlineStr">
-        <is>
-          <t>Censoring State</t>
-        </is>
-      </c>
-      <c r="H19" s="31" t="inlineStr">
-        <is>
-          <t>below_lod</t>
-        </is>
-      </c>
-      <c r="I19" s="31" t="inlineStr">
-        <is>
-          <t>Derived</t>
-        </is>
-      </c>
-      <c r="J19" s="31" t="inlineStr">
-        <is>
-          <t>SPONSOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="31" t="inlineStr">
-        <is>
-          <t>BM-2026-01</t>
-        </is>
-      </c>
-      <c r="B20" s="31" t="inlineStr">
-        <is>
-          <t>LB</t>
-        </is>
-      </c>
-      <c r="C20" s="31" t="inlineStr">
-        <is>
-          <t>BM-2026-01-002</t>
-        </is>
-      </c>
-      <c r="D20" s="31" t="inlineStr">
-        <is>
-          <t>LBSEQ</t>
-        </is>
-      </c>
-      <c r="E20" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="F20" s="36" t="inlineStr">
-        <is>
-          <t>CENSOR</t>
-        </is>
-      </c>
-      <c r="G20" s="31" t="inlineStr">
-        <is>
-          <t>Censoring State</t>
-        </is>
-      </c>
-      <c r="H20" s="31" t="inlineStr">
-        <is>
-          <t>detected_below_lloq</t>
-        </is>
-      </c>
-      <c r="I20" s="31" t="inlineStr">
-        <is>
-          <t>Derived</t>
-        </is>
-      </c>
-      <c r="J20" s="31" t="inlineStr">
-        <is>
-          <t>SPONSOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="31" t="inlineStr">
-        <is>
-          <t>BM-2026-01</t>
-        </is>
-      </c>
-      <c r="B21" s="31" t="inlineStr">
-        <is>
-          <t>LB</t>
-        </is>
-      </c>
-      <c r="C21" s="31" t="inlineStr">
-        <is>
-          <t>BM-2026-01-002</t>
-        </is>
-      </c>
-      <c r="D21" s="31" t="inlineStr">
-        <is>
-          <t>LBSEQ</t>
-        </is>
-      </c>
-      <c r="E21" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="F21" s="36" t="inlineStr">
-        <is>
-          <t>CENSOR</t>
-        </is>
-      </c>
-      <c r="G21" s="31" t="inlineStr">
-        <is>
-          <t>Censoring State</t>
-        </is>
-      </c>
-      <c r="H21" s="31" t="inlineStr">
-        <is>
-          <t>quantifiable</t>
-        </is>
-      </c>
-      <c r="I21" s="31" t="inlineStr">
-        <is>
-          <t>Derived</t>
-        </is>
-      </c>
-      <c r="J21" s="31" t="inlineStr">
         <is>
           <t>SPONSOR</t>
         </is>
@@ -6770,7 +6768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z5"/>
+  <dimension ref="A1:Z6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6804,7 +6802,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>The biomarker context layer. No values, no subjects, no dates - it describes why the LB records named in BMSRCDOM/BMSRCVAR/BMSRCVAL function as biomarkers.</t>
+          <t>The biomarker context layer. No values, no subjects, no dates - it describes why the LB records named in BMSRCDOM/BMSRCVAR/BMSRCVAL function as biomarkers. One row per claim: the Keller 2009 study supports a diagnostic and a prognostic (30-day outcome) claim.</t>
         </is>
       </c>
     </row>
@@ -7115,12 +7113,12 @@
       </c>
       <c r="I5" s="31" t="inlineStr">
         <is>
-          <t>MONITORING</t>
+          <t>DIAGNOSTIC</t>
         </is>
       </c>
       <c r="J5" s="31" t="inlineStr">
         <is>
-          <t>Acute myocardial infarction</t>
+          <t>acute myocardial infarction</t>
         </is>
       </c>
       <c r="K5" s="31" t="inlineStr">
@@ -7165,7 +7163,7 @@
       </c>
       <c r="S5" s="34" t="inlineStr">
         <is>
-          <t>TNNI3</t>
+          <t>TROPONI3</t>
         </is>
       </c>
       <c r="T5" s="34" t="inlineStr">
@@ -7199,6 +7197,138 @@
         </is>
       </c>
       <c r="Z5" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="31" t="inlineStr">
+        <is>
+          <t>BM-2026-01</t>
+        </is>
+      </c>
+      <c r="B6" s="31" t="inlineStr">
+        <is>
+          <t>BM</t>
+        </is>
+      </c>
+      <c r="C6" s="31" t="inlineStr">
+        <is>
+          <t>BM-002</t>
+        </is>
+      </c>
+      <c r="D6" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E6" s="31" t="inlineStr">
+        <is>
+          <t>Troponin I, cardiac muscle</t>
+        </is>
+      </c>
+      <c r="F6" s="31" t="inlineStr">
+        <is>
+          <t>UPKB:P19429</t>
+        </is>
+      </c>
+      <c r="G6" s="31" t="inlineStr">
+        <is>
+          <t>protein</t>
+        </is>
+      </c>
+      <c r="H6" s="31" t="inlineStr">
+        <is>
+          <t>Increased level of protein TNNI3/UPKB:P19429</t>
+        </is>
+      </c>
+      <c r="I6" s="31" t="inlineStr">
+        <is>
+          <t>PROGNOSTIC</t>
+        </is>
+      </c>
+      <c r="J6" s="31" t="inlineStr">
+        <is>
+          <t>acute myocardial infarction</t>
+        </is>
+      </c>
+      <c r="K6" s="31" t="inlineStr">
+        <is>
+          <t>DOID:5844</t>
+        </is>
+      </c>
+      <c r="L6" s="31" t="inlineStr">
+        <is>
+          <t>TnI-Ultra</t>
+        </is>
+      </c>
+      <c r="M6" s="31" t="inlineStr">
+        <is>
+          <t>Siemens Healthcare Diagnostics</t>
+        </is>
+      </c>
+      <c r="N6" s="31" t="inlineStr">
+        <is>
+          <t>ADVIA Centaur XP</t>
+        </is>
+      </c>
+      <c r="O6" s="31" t="inlineStr">
+        <is>
+          <t>IMMUNOASSAY</t>
+        </is>
+      </c>
+      <c r="P6" s="31" t="inlineStr">
+        <is>
+          <t>SERUM</t>
+        </is>
+      </c>
+      <c r="Q6" s="34" t="inlineStr">
+        <is>
+          <t>LB</t>
+        </is>
+      </c>
+      <c r="R6" s="34" t="inlineStr">
+        <is>
+          <t>LBTESTCD</t>
+        </is>
+      </c>
+      <c r="S6" s="34" t="inlineStr">
+        <is>
+          <t>TROPONI3</t>
+        </is>
+      </c>
+      <c r="T6" s="34" t="inlineStr">
+        <is>
+          <t>ASSAYNAM</t>
+        </is>
+      </c>
+      <c r="U6" s="34" t="inlineStr">
+        <is>
+          <t>TnI-Ultra</t>
+        </is>
+      </c>
+      <c r="V6" s="34" t="inlineStr">
+        <is>
+          <t>https://biocomputeobject.org/PLACEHOLDER_Troponin_I_tBCO/1.0.0</t>
+        </is>
+      </c>
+      <c r="W6" s="31" t="inlineStr">
+        <is>
+          <t>Admission value &gt; 0.04 ng/mL</t>
+        </is>
+      </c>
+      <c r="X6" s="31" t="inlineStr">
+        <is>
+          <t>PMID:19710485</t>
+        </is>
+      </c>
+      <c r="Y6" s="31" t="inlineStr">
+        <is>
+          <t>Sponsor Biomarker Review Board</t>
+        </is>
+      </c>
+      <c r="Z6" s="31" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>

--- a/examples/troponin_I/Troponin_I_SDTM.xlsx
+++ b/examples/troponin_I/Troponin_I_SDTM.xlsx
@@ -703,7 +703,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -846,7 +845,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
@@ -854,7 +852,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
@@ -984,7 +981,6 @@
       <c r="H18" s="14" t="n"/>
       <c r="I18" s="12" t="n"/>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
@@ -6093,6 +6089,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -6287,7 +6284,7 @@
       </c>
       <c r="H6" s="31" t="inlineStr">
         <is>
-          <t>https://biocomputeobject.org/PLACEHOLDER_Troponin_I_patient1_rBCO/1.0.0</t>
+          <t>https://biocomputeobject.org/PLACEHOLDER_Troponin_I_BM-2026-01-001_R-2026-0315-01_rBCO/1.0.0</t>
         </is>
       </c>
       <c r="I6" s="31" t="inlineStr">
@@ -6593,7 +6590,7 @@
       </c>
       <c r="H12" s="31" t="inlineStr">
         <is>
-          <t>https://biocomputeobject.org/PLACEHOLDER_Troponin_I_patient2_rBCO/1.0.0</t>
+          <t>https://biocomputeobject.org/PLACEHOLDER_Troponin_I_BM-2026-01-002_R-2026-0316-01_rBCO/1.0.0</t>
         </is>
       </c>
       <c r="I12" s="31" t="inlineStr">

--- a/examples/troponin_I/Troponin_I_SDTM.xlsx
+++ b/examples/troponin_I/Troponin_I_SDTM.xlsx
@@ -703,6 +703,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -845,6 +846,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
@@ -852,6 +854,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
@@ -981,6 +984,7 @@
       <c r="H18" s="14" t="n"/>
       <c r="I18" s="12" t="n"/>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
@@ -4762,6 +4766,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -5018,6 +5023,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -6803,6 +6809,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -7120,7 +7127,7 @@
       </c>
       <c r="K5" s="31" t="inlineStr">
         <is>
-          <t>DOID:5844</t>
+          <t>DOID:9408</t>
         </is>
       </c>
       <c r="L5" s="31" t="inlineStr">
@@ -7252,7 +7259,7 @@
       </c>
       <c r="K6" s="31" t="inlineStr">
         <is>
-          <t>DOID:5844</t>
+          <t>DOID:9408</t>
         </is>
       </c>
       <c r="L6" s="31" t="inlineStr">

--- a/examples/troponin_I/Troponin_I_SDTM.xlsx
+++ b/examples/troponin_I/Troponin_I_SDTM.xlsx
@@ -2047,7 +2047,11 @@
           <t>Original units in which the data were collected. The unit for LBORRES. Example: "g/L".</t>
         </is>
       </c>
-      <c r="G42" s="5" t="n"/>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>CDISC UNIT submission value (ug/L); the laboratory reports ng/mL, a CDISC synonym of the same unit.</t>
+        </is>
+      </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
           <t>Exp</t>
@@ -4423,7 +4427,11 @@
           <t>Citation supporting the claim: PMID, DOI, internal report. Evidence only; who asserted it is BMASSRT.</t>
         </is>
       </c>
-      <c r="G94" s="5" t="inlineStr"/>
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>As the study documents give it: here the full citation, since the context of use gives no PMID.</t>
+        </is>
+      </c>
       <c r="H94" s="7" t="inlineStr">
         <is>
           <t>Proposed</t>
@@ -4766,7 +4774,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -5023,7 +5030,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -5369,7 +5375,7 @@
       </c>
       <c r="K5" s="31" t="inlineStr">
         <is>
-          <t>ng/mL</t>
+          <t>ug/L</t>
         </is>
       </c>
       <c r="L5" s="31" t="inlineStr">
@@ -5387,7 +5393,7 @@
       </c>
       <c r="O5" s="31" t="inlineStr">
         <is>
-          <t>ng/mL</t>
+          <t>ug/L</t>
         </is>
       </c>
       <c r="P5" s="31" t="n"/>
@@ -5496,7 +5502,7 @@
       </c>
       <c r="K6" s="31" t="inlineStr">
         <is>
-          <t>ng/mL</t>
+          <t>ug/L</t>
         </is>
       </c>
       <c r="L6" s="31" t="inlineStr">
@@ -5514,7 +5520,7 @@
       </c>
       <c r="O6" s="31" t="inlineStr">
         <is>
-          <t>ng/mL</t>
+          <t>ug/L</t>
         </is>
       </c>
       <c r="P6" s="31" t="n"/>
@@ -5619,7 +5625,7 @@
       </c>
       <c r="K7" s="31" t="inlineStr">
         <is>
-          <t>ng/mL</t>
+          <t>ug/L</t>
         </is>
       </c>
       <c r="L7" s="31" t="inlineStr">
@@ -5637,7 +5643,7 @@
       </c>
       <c r="O7" s="31" t="inlineStr">
         <is>
-          <t>ng/mL</t>
+          <t>ug/L</t>
         </is>
       </c>
       <c r="P7" s="31" t="n"/>
@@ -5742,7 +5748,7 @@
       </c>
       <c r="K8" s="31" t="inlineStr">
         <is>
-          <t>ng/mL</t>
+          <t>ug/L</t>
         </is>
       </c>
       <c r="L8" s="31" t="inlineStr">
@@ -5758,7 +5764,7 @@
       <c r="N8" s="34" t="n"/>
       <c r="O8" s="31" t="inlineStr">
         <is>
-          <t>ng/mL</t>
+          <t>ug/L</t>
         </is>
       </c>
       <c r="P8" s="31" t="n"/>
@@ -5867,7 +5873,7 @@
       </c>
       <c r="K9" s="31" t="inlineStr">
         <is>
-          <t>ng/mL</t>
+          <t>ug/L</t>
         </is>
       </c>
       <c r="L9" s="31" t="inlineStr">
@@ -5885,7 +5891,7 @@
       </c>
       <c r="O9" s="31" t="inlineStr">
         <is>
-          <t>ng/mL</t>
+          <t>ug/L</t>
         </is>
       </c>
       <c r="P9" s="31" t="n"/>
@@ -5990,7 +5996,7 @@
       </c>
       <c r="K10" s="31" t="inlineStr">
         <is>
-          <t>ng/mL</t>
+          <t>ug/L</t>
         </is>
       </c>
       <c r="L10" s="31" t="inlineStr">
@@ -6008,7 +6014,7 @@
       </c>
       <c r="O10" s="31" t="inlineStr">
         <is>
-          <t>ng/mL</t>
+          <t>ug/L</t>
         </is>
       </c>
       <c r="P10" s="31" t="n"/>
@@ -6095,7 +6101,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -6809,7 +6814,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -7187,12 +7191,12 @@
       </c>
       <c r="W5" s="31" t="inlineStr">
         <is>
-          <t>Value &gt; 0.04 ng/mL AND rise or fall &gt;= 30% within 6 h</t>
+          <t>Value &gt; 0.04 ug/L AND rise or fall &gt;= 30% within 6 h</t>
         </is>
       </c>
       <c r="X5" s="31" t="inlineStr">
         <is>
-          <t>PMID:19710485</t>
+          <t>Keller T, Zeller T, Peetz D, et al. Sensitive troponin I assay in early diagnosis of acute myocardial infarction. N Engl J Med. 2009;361(9):868–877.</t>
         </is>
       </c>
       <c r="Y5" s="31" t="inlineStr">
@@ -7319,12 +7323,12 @@
       </c>
       <c r="W6" s="31" t="inlineStr">
         <is>
-          <t>Admission value &gt; 0.04 ng/mL</t>
+          <t>Admission value &gt; 0.04 ug/L</t>
         </is>
       </c>
       <c r="X6" s="31" t="inlineStr">
         <is>
-          <t>PMID:19710485</t>
+          <t>Keller T, Zeller T, Peetz D, et al. Sensitive troponin I assay in early diagnosis of acute myocardial infarction. N Engl J Med. 2009;361(9):868–877.</t>
         </is>
       </c>
       <c r="Y6" s="31" t="inlineStr">
